--- a/data-cleaning/verified/数据清洗审计.xlsx
+++ b/data-cleaning/verified/数据清洗审计.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>film-records-conservative-v2</t>
+          <t>film-records-physical-codes-v3</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>流水号不是物理编号；F/B几何、独立物理管总数未确认；W/Q属于同管不同部位</t>
+          <t>编码=位置+Q/W字母尾，永久唯一；流水号只在溯源列；F/B几何、独立物理管总数未确认</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F004-W001</t>
+          <t>1G-GGRQ-GQ-L002-F004-W</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F005-W002</t>
+          <t>1G-GGRQ-GQ-L002-F005-W</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F006-W003</t>
+          <t>1G-GGRQ-GQ-L002-F006-W</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F007-W004</t>
+          <t>1G-GGRQ-GQ-L002-F007-W</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F008-W005</t>
+          <t>1G-GGRQ-GQ-L002-F008-W</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F009-W006</t>
+          <t>1G-GGRQ-GQ-L002-F009-W</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F010-W007</t>
+          <t>1G-GGRQ-GQ-L002-F010-W</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F014-W008</t>
+          <t>1G-GGRQ-GQ-L002-F014-W</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F015-W009</t>
+          <t>1G-GGRQ-GQ-L002-F015-W</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F016-W010</t>
+          <t>1G-GGRQ-GQ-L002-F016-W</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F017-W011</t>
+          <t>1G-GGRQ-GQ-L002-F017-W</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F018-W012</t>
+          <t>1G-GGRQ-GQ-L002-F018-W</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F019-W013</t>
+          <t>1G-GGRQ-GQ-L002-F019-W</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F020-W014</t>
+          <t>1G-GGRQ-GQ-L002-F020-W</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F021-W015</t>
+          <t>1G-GGRQ-GQ-L002-F021-W</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F022-W016</t>
+          <t>1G-GGRQ-GQ-L002-F022-W</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F004-W017</t>
+          <t>1G-GGRQ-GQ-L031-F004-W</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F005-W018</t>
+          <t>1G-GGRQ-GQ-L031-F005-W</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F006-W019</t>
+          <t>1G-GGRQ-GQ-L031-F006-W</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F007-W020</t>
+          <t>1G-GGRQ-GQ-L031-F007-W</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F008-W021</t>
+          <t>1G-GGRQ-GQ-L031-F008-W</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F009-W022</t>
+          <t>1G-GGRQ-GQ-L031-F009-W</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F010-W023</t>
+          <t>1G-GGRQ-GQ-L031-F010-W</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F014-W024</t>
+          <t>1G-GGRQ-GQ-L031-F014-W</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F015-W025</t>
+          <t>1G-GGRQ-GQ-L031-F015-W</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F016-W026</t>
+          <t>1G-GGRQ-GQ-L031-F016-W</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F017-W027</t>
+          <t>1G-GGRQ-GQ-L031-F017-W</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F018-W028</t>
+          <t>1G-GGRQ-GQ-L031-F018-W</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F019-W029</t>
+          <t>1G-GGRQ-GQ-L031-F019-W</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F020-W030</t>
+          <t>1G-GGRQ-GQ-L031-F020-W</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F021-W031</t>
+          <t>1G-GGRQ-GQ-L031-F021-W</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F022-W032</t>
+          <t>1G-GGRQ-GQ-L031-F022-W</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F001-W033</t>
+          <t>1G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F001-W034</t>
+          <t>1G-GGRQ-GQ-L002-F001-W</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F001-W035</t>
+          <t>1G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F001-W036</t>
+          <t>1G-GGRQ-GQ-L004-F001-W</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F001-W037</t>
+          <t>1G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F001-W038</t>
+          <t>1G-GGRQ-GQ-L006-F001-W</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F001-W039</t>
+          <t>1G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F001-W040</t>
+          <t>1G-GGRQ-GQ-L008-F001-W</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F001-W041</t>
+          <t>1G-GGRQ-GQ-L009-F001-W</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F001-W042</t>
+          <t>1G-GGRQ-GQ-L010-F001-W</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F001-W043</t>
+          <t>1G-GGRQ-GQ-L011-F001-W</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F001-W044</t>
+          <t>1G-GGRQ-GQ-L012-F001-W</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F001-W045</t>
+          <t>1G-GGRQ-GQ-L013-F001-W</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F001-W046</t>
+          <t>1G-GGRQ-GQ-L014-F001-W</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F001-W047</t>
+          <t>1G-GGRQ-GQ-L015-F001-W</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F001-W048</t>
+          <t>1G-GGRQ-GQ-L016-F001-W</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F001-W049</t>
+          <t>1G-GGRQ-GQ-L017-F001-W</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F001-W050</t>
+          <t>1G-GGRQ-GQ-L018-F001-W</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F001-W051</t>
+          <t>1G-GGRQ-GQ-L019-F001-W</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F001-W052</t>
+          <t>1G-GGRQ-GQ-L020-F001-W</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F001-W053</t>
+          <t>1G-GGRQ-GQ-L021-F001-W</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F001-W054</t>
+          <t>1G-GGRQ-GQ-L022-F001-W</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F001-W055</t>
+          <t>1G-GGRQ-GQ-L023-F001-W</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F001-W056</t>
+          <t>1G-GGRQ-GQ-L024-F001-W</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F001-W057</t>
+          <t>1G-GGRQ-GQ-L025-F001-W</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F001-W058</t>
+          <t>1G-GGRQ-GQ-L026-F001-W</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F001-W059</t>
+          <t>1G-GGRQ-GQ-L028-F001-W</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F001-W060</t>
+          <t>1G-GGRQ-GQ-L029-F001-W</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F001-W061</t>
+          <t>1G-GGRQ-GQ-L030-F001-W</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F001-W062</t>
+          <t>1G-GGRQ-GQ-L031-F001-W</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F001-W063</t>
+          <t>1G-GGRQ-GQ-L032-F001-W</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W064</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -8025,7 +8025,7 @@
       <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W065</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F002-W066</t>
+          <t>1G-GGRQ-GQ-L002-F002-W</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -8241,7 +8241,7 @@
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F003-W067</t>
+          <t>1G-GGRQ-GQ-L002-F003-W</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W068</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W069</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F002-W070</t>
+          <t>1G-GGRQ-GQ-L004-F002-W</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F003-W071</t>
+          <t>1G-GGRQ-GQ-L004-F003-W</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F002-W072</t>
+          <t>1G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W073</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -9005,7 +9005,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F002-W074</t>
+          <t>1G-GGRQ-GQ-L006-F002-W</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F003-W075</t>
+          <t>1G-GGRQ-GQ-L006-F003-W</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
@@ -9221,7 +9221,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W076</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W077</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
@@ -9437,7 +9437,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F002-W078</t>
+          <t>1G-GGRQ-GQ-L008-F002-W</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F003-W079</t>
+          <t>1G-GGRQ-GQ-L008-F003-W</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
@@ -9653,7 +9653,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F002-W080</t>
+          <t>1G-GGRQ-GQ-L009-F002-W</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F003-W081</t>
+          <t>1G-GGRQ-GQ-L009-F003-W</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F002-W082</t>
+          <t>1G-GGRQ-GQ-L010-F002-W</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F003-W083</t>
+          <t>1G-GGRQ-GQ-L010-F003-W</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
@@ -10089,7 +10089,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F002-W084</t>
+          <t>1G-GGRQ-GQ-L011-F002-W</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F003-W085</t>
+          <t>1G-GGRQ-GQ-L011-F003-W</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
@@ -10305,7 +10305,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F002-W086</t>
+          <t>1G-GGRQ-GQ-L012-F002-W</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       <c r="J89" s="3" t="inlineStr"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F003-W087</t>
+          <t>1G-GGRQ-GQ-L012-F003-W</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F002-W088</t>
+          <t>1G-GGRQ-GQ-L013-F002-W</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
       <c r="J91" s="3" t="inlineStr"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F003-W089</t>
+          <t>1G-GGRQ-GQ-L013-F003-W</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
@@ -10741,7 +10741,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F002-W090</t>
+          <t>1G-GGRQ-GQ-L014-F002-W</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       <c r="J93" s="3" t="inlineStr"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F003-W091</t>
+          <t>1G-GGRQ-GQ-L014-F003-W</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
@@ -10957,7 +10957,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F002-W092</t>
+          <t>1G-GGRQ-GQ-L015-F002-W</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       <c r="J95" s="3" t="inlineStr"/>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F003-W093</t>
+          <t>1G-GGRQ-GQ-L015-F003-W</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
@@ -11173,7 +11173,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F002-W094</t>
+          <t>1G-GGRQ-GQ-L016-F002-W</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       <c r="J97" s="3" t="inlineStr"/>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F003-W095</t>
+          <t>1G-GGRQ-GQ-L016-F003-W</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
@@ -11389,7 +11389,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F002-W096</t>
+          <t>1G-GGRQ-GQ-L017-F002-W</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       <c r="J99" s="3" t="inlineStr"/>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F003-W097</t>
+          <t>1G-GGRQ-GQ-L017-F003-W</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
@@ -11605,7 +11605,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F002-W098</t>
+          <t>1G-GGRQ-GQ-L018-F002-W</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       <c r="J101" s="3" t="inlineStr"/>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F003-W099</t>
+          <t>1G-GGRQ-GQ-L018-F003-W</t>
         </is>
       </c>
       <c r="L101" s="3" t="inlineStr">
@@ -11821,7 +11821,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F002-W100</t>
+          <t>1G-GGRQ-GQ-L019-F002-W</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       <c r="J103" s="3" t="inlineStr"/>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F003-W101</t>
+          <t>1G-GGRQ-GQ-L019-F003-W</t>
         </is>
       </c>
       <c r="L103" s="3" t="inlineStr">
@@ -12037,7 +12037,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F002-W102</t>
+          <t>1G-GGRQ-GQ-L020-F002-W</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -12145,7 +12145,7 @@
       <c r="J105" s="3" t="inlineStr"/>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F003-W103</t>
+          <t>1G-GGRQ-GQ-L020-F003-W</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
@@ -12253,7 +12253,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F002-W104</t>
+          <t>1G-GGRQ-GQ-L021-F002-W</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F003-W105</t>
+          <t>1G-GGRQ-GQ-L021-F003-W</t>
         </is>
       </c>
       <c r="L107" s="3" t="inlineStr">
@@ -12469,7 +12469,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F002-W106</t>
+          <t>1G-GGRQ-GQ-L022-F002-W</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       <c r="J109" s="3" t="inlineStr"/>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F003-W107</t>
+          <t>1G-GGRQ-GQ-L022-F003-W</t>
         </is>
       </c>
       <c r="L109" s="3" t="inlineStr">
@@ -12685,7 +12685,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F002-W108</t>
+          <t>1G-GGRQ-GQ-L023-F002-W</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -12793,7 +12793,7 @@
       <c r="J111" s="3" t="inlineStr"/>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F003-W109</t>
+          <t>1G-GGRQ-GQ-L023-F003-W</t>
         </is>
       </c>
       <c r="L111" s="3" t="inlineStr">
@@ -12901,7 +12901,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F002-W110</t>
+          <t>1G-GGRQ-GQ-L024-F002-W</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -13009,7 +13009,7 @@
       <c r="J113" s="3" t="inlineStr"/>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F003-W111</t>
+          <t>1G-GGRQ-GQ-L024-F003-W</t>
         </is>
       </c>
       <c r="L113" s="3" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F002-W112</t>
+          <t>1G-GGRQ-GQ-L025-F002-W</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -13229,7 +13229,7 @@
       <c r="J115" s="3" t="inlineStr"/>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F003-W113</t>
+          <t>1G-GGRQ-GQ-L025-F003-W</t>
         </is>
       </c>
       <c r="L115" s="3" t="inlineStr">
@@ -13337,7 +13337,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F002-W114</t>
+          <t>1G-GGRQ-GQ-L026-F002-W</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -13445,7 +13445,7 @@
       <c r="J117" s="3" t="inlineStr"/>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F003-W115</t>
+          <t>1G-GGRQ-GQ-L026-F003-W</t>
         </is>
       </c>
       <c r="L117" s="3" t="inlineStr">
@@ -13553,7 +13553,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F002-W116</t>
+          <t>1G-GGRQ-GQ-L027-F002-W</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -13661,7 +13661,7 @@
       <c r="J119" s="3" t="inlineStr"/>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F003-W117</t>
+          <t>1G-GGRQ-GQ-L027-F003-W</t>
         </is>
       </c>
       <c r="L119" s="3" t="inlineStr">
@@ -13769,7 +13769,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F002-W118</t>
+          <t>1G-GGRQ-GQ-L028-F002-W</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -13877,7 +13877,7 @@
       <c r="J121" s="3" t="inlineStr"/>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F003-W119</t>
+          <t>1G-GGRQ-GQ-L028-F003-W</t>
         </is>
       </c>
       <c r="L121" s="3" t="inlineStr">
@@ -13985,7 +13985,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F002-W120</t>
+          <t>1G-GGRQ-GQ-L029-F002-W</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -14093,7 +14093,7 @@
       <c r="J123" s="3" t="inlineStr"/>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F003-W121</t>
+          <t>1G-GGRQ-GQ-L029-F003-W</t>
         </is>
       </c>
       <c r="L123" s="3" t="inlineStr">
@@ -14201,7 +14201,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F002-W122</t>
+          <t>1G-GGRQ-GQ-L030-F002-W</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -14309,7 +14309,7 @@
       <c r="J125" s="3" t="inlineStr"/>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F003-W123</t>
+          <t>1G-GGRQ-GQ-L030-F003-W</t>
         </is>
       </c>
       <c r="L125" s="3" t="inlineStr">
@@ -14417,7 +14417,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F002-W124</t>
+          <t>1G-GGRQ-GQ-L031-F002-W</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -14525,7 +14525,7 @@
       <c r="J127" s="3" t="inlineStr"/>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F003-W125</t>
+          <t>1G-GGRQ-GQ-L031-F003-W</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
@@ -14633,7 +14633,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F002-W126</t>
+          <t>1G-GGRQ-GQ-L032-F002-W</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       <c r="J129" s="3" t="inlineStr"/>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F003-W127</t>
+          <t>1G-GGRQ-GQ-L032-F003-W</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
@@ -14849,7 +14849,7 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W128</t>
+          <t>1G-GGRQ-GQ-L001-B001-W</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -14957,7 +14957,7 @@
       <c r="J131" s="3" t="inlineStr"/>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W129</t>
+          <t>1G-GGRQ-GQ-L002-B001-W</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
@@ -15065,7 +15065,7 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W130</t>
+          <t>1G-GGRQ-GQ-L003-B001-W</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -15173,7 +15173,7 @@
       <c r="J133" s="3" t="inlineStr"/>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W131</t>
+          <t>1G-GGRQ-GQ-L004-B001-W</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
@@ -15281,7 +15281,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W132</t>
+          <t>1G-GGRQ-GQ-L005-B001-W</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -15389,7 +15389,7 @@
       <c r="J135" s="3" t="inlineStr"/>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W133</t>
+          <t>1G-GGRQ-GQ-L006-B001-W</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
@@ -15497,7 +15497,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W134</t>
+          <t>1G-GGRQ-GQ-L007-B001-W</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -15605,7 +15605,7 @@
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W135</t>
+          <t>1G-GGRQ-GQ-L008-B001-W</t>
         </is>
       </c>
       <c r="L137" s="3" t="inlineStr">
@@ -15713,7 +15713,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W136</t>
+          <t>1G-GGRQ-GQ-L009-B001-W</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -15821,7 +15821,7 @@
       <c r="J139" s="3" t="inlineStr"/>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W137</t>
+          <t>1G-GGRQ-GQ-L010-B001-W</t>
         </is>
       </c>
       <c r="L139" s="3" t="inlineStr">
@@ -15929,7 +15929,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W138</t>
+          <t>1G-GGRQ-GQ-L011-B001-W</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -16037,7 +16037,7 @@
       <c r="J141" s="3" t="inlineStr"/>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W139</t>
+          <t>1G-GGRQ-GQ-L012-B001-W</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr">
@@ -16145,7 +16145,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W140</t>
+          <t>1G-GGRQ-GQ-L013-B001-W</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -16253,7 +16253,7 @@
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W141</t>
+          <t>1G-GGRQ-GQ-L014-B001-W</t>
         </is>
       </c>
       <c r="L143" s="3" t="inlineStr">
@@ -16361,7 +16361,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W142</t>
+          <t>1G-GGRQ-GQ-L015-B001-W</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -16469,7 +16469,7 @@
       <c r="J145" s="3" t="inlineStr"/>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W143</t>
+          <t>1G-GGRQ-GQ-L016-B001-W</t>
         </is>
       </c>
       <c r="L145" s="3" t="inlineStr">
@@ -16577,7 +16577,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W144</t>
+          <t>1G-GGRQ-GQ-L017-B001-W</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -16685,7 +16685,7 @@
       <c r="J147" s="3" t="inlineStr"/>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W145</t>
+          <t>1G-GGRQ-GQ-L018-B001-W</t>
         </is>
       </c>
       <c r="L147" s="3" t="inlineStr">
@@ -16793,7 +16793,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W146</t>
+          <t>1G-GGRQ-GQ-L019-B001-W</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -16901,7 +16901,7 @@
       <c r="J149" s="3" t="inlineStr"/>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W147</t>
+          <t>1G-GGRQ-GQ-L020-B001-W</t>
         </is>
       </c>
       <c r="L149" s="3" t="inlineStr">
@@ -17009,7 +17009,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W148</t>
+          <t>1G-GGRQ-GQ-L021-B001-W</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -17117,7 +17117,7 @@
       <c r="J151" s="3" t="inlineStr"/>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W149</t>
+          <t>1G-GGRQ-GQ-L022-B001-W</t>
         </is>
       </c>
       <c r="L151" s="3" t="inlineStr">
@@ -17225,7 +17225,7 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W150</t>
+          <t>1G-GGRQ-GQ-L023-B001-W</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -17333,7 +17333,7 @@
       <c r="J153" s="3" t="inlineStr"/>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W151</t>
+          <t>1G-GGRQ-GQ-L024-B001-W</t>
         </is>
       </c>
       <c r="L153" s="3" t="inlineStr">
@@ -17441,7 +17441,7 @@
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W152</t>
+          <t>1G-GGRQ-GQ-L025-B001-W</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -17549,7 +17549,7 @@
       <c r="J155" s="3" t="inlineStr"/>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W153</t>
+          <t>1G-GGRQ-GQ-L026-B001-W</t>
         </is>
       </c>
       <c r="L155" s="3" t="inlineStr">
@@ -17657,7 +17657,7 @@
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W154</t>
+          <t>1G-GGRQ-GQ-L027-B001-W</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -17765,7 +17765,7 @@
       <c r="J157" s="3" t="inlineStr"/>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W155</t>
+          <t>1G-GGRQ-GQ-L028-B001-W</t>
         </is>
       </c>
       <c r="L157" s="3" t="inlineStr">
@@ -17873,7 +17873,7 @@
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W156</t>
+          <t>1G-GGRQ-GQ-L029-B001-W</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -17981,7 +17981,7 @@
       <c r="J159" s="3" t="inlineStr"/>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W157</t>
+          <t>1G-GGRQ-GQ-L030-B001-W</t>
         </is>
       </c>
       <c r="L159" s="3" t="inlineStr">
@@ -18089,7 +18089,7 @@
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W158</t>
+          <t>1G-GGRQ-GQ-L031-B001-W</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -18197,7 +18197,7 @@
       <c r="J161" s="3" t="inlineStr"/>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W159</t>
+          <t>1G-GGRQ-GQ-L032-B001-W</t>
         </is>
       </c>
       <c r="L161" s="3" t="inlineStr">
@@ -18313,7 +18313,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F001-W001</t>
+          <t>1G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -18425,7 +18425,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W002</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="L163" s="3" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W003</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F004-W004</t>
+          <t>1G-GGRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="L165" s="3" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F005-W005</t>
+          <t>1G-GGRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F006-W006</t>
+          <t>1G-GGRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="L167" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F007-W007</t>
+          <t>1G-GGRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F008-W008</t>
+          <t>1G-GGRQ-GQ-L001-F008-W</t>
         </is>
       </c>
       <c r="L169" s="3" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F009-W009</t>
+          <t>1G-GGRQ-GQ-L001-F009-W</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F010-W010</t>
+          <t>1G-GGRQ-GQ-L001-F010-W</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F011-W011</t>
+          <t>1G-GGRQ-GQ-L001-F011-W</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F012-W012</t>
+          <t>1G-GGRQ-GQ-L001-F012-W</t>
         </is>
       </c>
       <c r="L173" s="3" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F001-W013</t>
+          <t>1G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W014</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="L175" s="3" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W015</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -19993,7 +19993,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F004-W016</t>
+          <t>1G-GGRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="L177" s="3" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F005-W017</t>
+          <t>1G-GGRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -20217,7 +20217,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F006-W018</t>
+          <t>1G-GGRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="L179" s="3" t="inlineStr">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F007-W019</t>
+          <t>1G-GGRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F008-W020</t>
+          <t>1G-GGRQ-GQ-L003-F008-W</t>
         </is>
       </c>
       <c r="L181" s="3" t="inlineStr">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F009-W021</t>
+          <t>1G-GGRQ-GQ-L003-F009-W</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">
@@ -20665,7 +20665,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F010-W022</t>
+          <t>1G-GGRQ-GQ-L003-F010-W</t>
         </is>
       </c>
       <c r="L183" s="3" t="inlineStr">
@@ -20777,7 +20777,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F011-W023</t>
+          <t>1G-GGRQ-GQ-L003-F011-W</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F012-W024</t>
+          <t>1G-GGRQ-GQ-L003-F012-W</t>
         </is>
       </c>
       <c r="L185" s="3" t="inlineStr">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F001-W025</t>
+          <t>1G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F002-W026</t>
+          <t>1G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="L187" s="3" t="inlineStr">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W027</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F004-W028</t>
+          <t>1G-GGRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="L189" s="3" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F005-W029</t>
+          <t>1G-GGRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F006-W030</t>
+          <t>1G-GGRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="L191" s="3" t="inlineStr">
@@ -21673,7 +21673,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F007-W031</t>
+          <t>1G-GGRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F008-W032</t>
+          <t>1G-GGRQ-GQ-L005-F008-W</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
@@ -21897,7 +21897,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F009-W033</t>
+          <t>1G-GGRQ-GQ-L005-F009-W</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
@@ -22009,7 +22009,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F010-W034</t>
+          <t>1G-GGRQ-GQ-L005-F010-W</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F011-W035</t>
+          <t>1G-GGRQ-GQ-L005-F011-W</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F012-W036</t>
+          <t>1G-GGRQ-GQ-L005-F012-W</t>
         </is>
       </c>
       <c r="L197" s="3" t="inlineStr">
@@ -22345,7 +22345,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F001-W037</t>
+          <t>1G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
@@ -22457,7 +22457,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W038</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W039</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -22681,7 +22681,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F004-W040</t>
+          <t>1G-GGRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="L201" s="3" t="inlineStr">
@@ -22793,7 +22793,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F005-W041</t>
+          <t>1G-GGRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F006-W042</t>
+          <t>1G-GGRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="L203" s="3" t="inlineStr">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F007-W043</t>
+          <t>1G-GGRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
@@ -23129,7 +23129,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F008-W044</t>
+          <t>1G-GGRQ-GQ-L007-F008-W</t>
         </is>
       </c>
       <c r="L205" s="3" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F009-W045</t>
+          <t>1G-GGRQ-GQ-L007-F009-W</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F010-W046</t>
+          <t>1G-GGRQ-GQ-L007-F010-W</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F011-W047</t>
+          <t>1G-GGRQ-GQ-L007-F011-W</t>
         </is>
       </c>
       <c r="L208" s="2" t="inlineStr">
@@ -23577,7 +23577,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F012-W048</t>
+          <t>1G-GGRQ-GQ-L007-F012-W</t>
         </is>
       </c>
       <c r="L209" s="3" t="inlineStr">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F001-W049</t>
+          <t>1G-GGRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="L210" s="2" t="inlineStr">
@@ -23801,7 +23801,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F002-W050</t>
+          <t>1G-GGRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
@@ -23913,7 +23913,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F003-W051</t>
+          <t>1G-GGRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
@@ -24025,7 +24025,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F004-W052</t>
+          <t>1G-GGRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr">
@@ -24137,7 +24137,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F005-W053</t>
+          <t>1G-GGRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -24249,7 +24249,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F006-W054</t>
+          <t>1G-GGRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="L215" s="3" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F007-W055</t>
+          <t>1G-GGRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="L216" s="2" t="inlineStr">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F008-W056</t>
+          <t>1G-GGRQ-GQ-R001-F008-W</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F009-W057</t>
+          <t>1G-GGRQ-GQ-R001-F009-W</t>
         </is>
       </c>
       <c r="L218" s="2" t="inlineStr">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F010-W058</t>
+          <t>1G-GGRQ-GQ-R001-F010-W</t>
         </is>
       </c>
       <c r="L219" s="3" t="inlineStr">
@@ -24809,7 +24809,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F011-W059</t>
+          <t>1G-GGRQ-GQ-R001-F011-W</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
@@ -24921,7 +24921,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F012-W060</t>
+          <t>1G-GGRQ-GQ-R001-F012-W</t>
         </is>
       </c>
       <c r="L221" s="3" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F001-W061</t>
+          <t>1G-GGRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="L222" s="2" t="inlineStr">
@@ -25145,7 +25145,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F002-W062</t>
+          <t>1G-GGRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F003-W063</t>
+          <t>1G-GGRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="L224" s="2" t="inlineStr">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F004-W064</t>
+          <t>1G-GGRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="L225" s="3" t="inlineStr">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F005-W065</t>
+          <t>1G-GGRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="L226" s="2" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F006-W066</t>
+          <t>1G-GGRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="L227" s="3" t="inlineStr">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F007-W067</t>
+          <t>1G-GGRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="L228" s="2" t="inlineStr">
@@ -25817,7 +25817,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F008-W068</t>
+          <t>1G-GGRQ-GQ-R003-F008-W</t>
         </is>
       </c>
       <c r="L229" s="3" t="inlineStr">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F009-W069</t>
+          <t>1G-GGRQ-GQ-R003-F009-W</t>
         </is>
       </c>
       <c r="L230" s="2" t="inlineStr">
@@ -26041,7 +26041,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F010-W070</t>
+          <t>1G-GGRQ-GQ-R003-F010-W</t>
         </is>
       </c>
       <c r="L231" s="3" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F011-W071</t>
+          <t>1G-GGRQ-GQ-R003-F011-W</t>
         </is>
       </c>
       <c r="L232" s="2" t="inlineStr">
@@ -26265,7 +26265,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F012-W072</t>
+          <t>1G-GGRQ-GQ-R003-F012-W</t>
         </is>
       </c>
       <c r="L233" s="3" t="inlineStr">
@@ -26377,7 +26377,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F001-W073</t>
+          <t>1G-GGRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="L234" s="2" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F002-W074</t>
+          <t>1G-GGRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="L235" s="3" t="inlineStr">
@@ -26601,7 +26601,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F003-W075</t>
+          <t>1G-GGRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="L236" s="2" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F004-W076</t>
+          <t>1G-GGRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="L237" s="3" t="inlineStr">
@@ -26825,7 +26825,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F005-W077</t>
+          <t>1G-GGRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="L238" s="2" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F006-W078</t>
+          <t>1G-GGRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="L239" s="3" t="inlineStr">
@@ -27049,7 +27049,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F007-W079</t>
+          <t>1G-GGRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="L240" s="2" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F008-W080</t>
+          <t>1G-GGRQ-GQ-R005-F008-W</t>
         </is>
       </c>
       <c r="L241" s="3" t="inlineStr">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F009-W081</t>
+          <t>1G-GGRQ-GQ-R005-F009-W</t>
         </is>
       </c>
       <c r="L242" s="2" t="inlineStr">
@@ -27385,7 +27385,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F010-W082</t>
+          <t>1G-GGRQ-GQ-R005-F010-W</t>
         </is>
       </c>
       <c r="L243" s="3" t="inlineStr">
@@ -27497,7 +27497,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F011-W083</t>
+          <t>1G-GGRQ-GQ-R005-F011-W</t>
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F012-W084</t>
+          <t>1G-GGRQ-GQ-R005-F012-W</t>
         </is>
       </c>
       <c r="L245" s="3" t="inlineStr">
@@ -27721,7 +27721,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F001-W085</t>
+          <t>1G-GGRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="L246" s="2" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F002-W086</t>
+          <t>1G-GGRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="L247" s="3" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F003-W087</t>
+          <t>1G-GGRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="L248" s="2" t="inlineStr">
@@ -28057,7 +28057,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F004-W088</t>
+          <t>1G-GGRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="L249" s="3" t="inlineStr">
@@ -28169,7 +28169,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F005-W089</t>
+          <t>1G-GGRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
@@ -28281,7 +28281,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F006-W090</t>
+          <t>1G-GGRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="L251" s="3" t="inlineStr">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F007-W091</t>
+          <t>1G-GGRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
@@ -28505,7 +28505,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F008-W092</t>
+          <t>1G-GGRQ-GQ-R007-F008-W</t>
         </is>
       </c>
       <c r="L253" s="3" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F009-W093</t>
+          <t>1G-GGRQ-GQ-R007-F009-W</t>
         </is>
       </c>
       <c r="L254" s="2" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F010-W094</t>
+          <t>1G-GGRQ-GQ-R007-F010-W</t>
         </is>
       </c>
       <c r="L255" s="3" t="inlineStr">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F011-W095</t>
+          <t>1G-GGRQ-GQ-R007-F011-W</t>
         </is>
       </c>
       <c r="L256" s="2" t="inlineStr">
@@ -28953,7 +28953,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F012-W096</t>
+          <t>1G-GGRQ-GQ-R007-F012-W</t>
         </is>
       </c>
       <c r="L257" s="3" t="inlineStr">
@@ -29065,7 +29065,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F001-W097</t>
+          <t>1G-GZRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="L258" s="2" t="inlineStr">
@@ -29181,7 +29181,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F002-W098</t>
+          <t>1G-GZRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="L259" s="3" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F003-W099</t>
+          <t>1G-GZRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F004-W100</t>
+          <t>1G-GZRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="L261" s="3" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F005-W101</t>
+          <t>1G-GZRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="L262" s="2" t="inlineStr">
@@ -29645,7 +29645,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F006-W102</t>
+          <t>1G-GZRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="L263" s="3" t="inlineStr">
@@ -29761,7 +29761,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F007-W103</t>
+          <t>1G-GZRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="L264" s="2" t="inlineStr">
@@ -29877,7 +29877,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F001-W104</t>
+          <t>1G-GZRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="L265" s="3" t="inlineStr">
@@ -29993,7 +29993,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F002-W105</t>
+          <t>1G-GZRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="L266" s="2" t="inlineStr">
@@ -30109,7 +30109,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F003-W106</t>
+          <t>1G-GZRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="L267" s="3" t="inlineStr">
@@ -30225,7 +30225,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F004-W107</t>
+          <t>1G-GZRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="L268" s="2" t="inlineStr">
@@ -30341,7 +30341,7 @@
       </c>
       <c r="K269" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F005-W108</t>
+          <t>1G-GZRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="L269" s="3" t="inlineStr">
@@ -30457,7 +30457,7 @@
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F006-W109</t>
+          <t>1G-GZRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="L270" s="2" t="inlineStr">
@@ -30573,7 +30573,7 @@
       </c>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F007-W110</t>
+          <t>1G-GZRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="L271" s="3" t="inlineStr">
@@ -30689,7 +30689,7 @@
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F001-W111</t>
+          <t>1G-GZRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="L272" s="2" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="K273" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F002-W112</t>
+          <t>1G-GZRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="L273" s="3" t="inlineStr">
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F003-W113</t>
+          <t>1G-GZRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="L274" s="2" t="inlineStr">
@@ -31037,7 +31037,7 @@
       </c>
       <c r="K275" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F004-W114</t>
+          <t>1G-GZRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="L275" s="3" t="inlineStr">
@@ -31153,7 +31153,7 @@
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F005-W115</t>
+          <t>1G-GZRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="L276" s="2" t="inlineStr">
@@ -31269,7 +31269,7 @@
       </c>
       <c r="K277" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F006-W116</t>
+          <t>1G-GZRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="L277" s="3" t="inlineStr">
@@ -31385,7 +31385,7 @@
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F007-W117</t>
+          <t>1G-GZRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr">
@@ -31501,7 +31501,7 @@
       </c>
       <c r="K279" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F001-W118</t>
+          <t>1G-GZRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="L279" s="3" t="inlineStr">
@@ -31617,7 +31617,7 @@
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F002-W119</t>
+          <t>1G-GZRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="L280" s="2" t="inlineStr">
@@ -31733,7 +31733,7 @@
       </c>
       <c r="K281" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F003-W120</t>
+          <t>1G-GZRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="L281" s="3" t="inlineStr">
@@ -31849,7 +31849,7 @@
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F004-W121</t>
+          <t>1G-GZRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="L282" s="2" t="inlineStr">
@@ -31965,7 +31965,7 @@
       </c>
       <c r="K283" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F005-W122</t>
+          <t>1G-GZRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="L283" s="3" t="inlineStr">
@@ -32081,7 +32081,7 @@
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F006-W123</t>
+          <t>1G-GZRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="L284" s="2" t="inlineStr">
@@ -32197,7 +32197,7 @@
       </c>
       <c r="K285" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F007-W124</t>
+          <t>1G-GZRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="L285" s="3" t="inlineStr">
@@ -32313,7 +32313,7 @@
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F001-W125</t>
+          <t>1G-GZRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="L286" s="2" t="inlineStr">
@@ -32429,7 +32429,7 @@
       </c>
       <c r="K287" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F002-W126</t>
+          <t>1G-GZRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="L287" s="3" t="inlineStr">
@@ -32545,7 +32545,7 @@
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F003-W127</t>
+          <t>1G-GZRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="L288" s="2" t="inlineStr">
@@ -32661,7 +32661,7 @@
       </c>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F004-W128</t>
+          <t>1G-GZRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="L289" s="3" t="inlineStr">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F005-W129</t>
+          <t>1G-GZRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="L290" s="2" t="inlineStr">
@@ -32893,7 +32893,7 @@
       </c>
       <c r="K291" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F006-W130</t>
+          <t>1G-GZRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="L291" s="3" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F007-W131</t>
+          <t>1G-GZRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="L292" s="2" t="inlineStr">
@@ -33125,7 +33125,7 @@
       </c>
       <c r="K293" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F001-W132</t>
+          <t>1G-GZRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="L293" s="3" t="inlineStr">
@@ -33241,7 +33241,7 @@
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F002-W133</t>
+          <t>1G-GZRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="L294" s="2" t="inlineStr">
@@ -33357,7 +33357,7 @@
       </c>
       <c r="K295" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F003-W134</t>
+          <t>1G-GZRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="L295" s="3" t="inlineStr">
@@ -33473,7 +33473,7 @@
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F004-W135</t>
+          <t>1G-GZRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="L296" s="2" t="inlineStr">
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K297" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F005-W136</t>
+          <t>1G-GZRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="L297" s="3" t="inlineStr">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F006-W137</t>
+          <t>1G-GZRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="L298" s="2" t="inlineStr">
@@ -33821,7 +33821,7 @@
       </c>
       <c r="K299" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F007-W138</t>
+          <t>1G-GZRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="L299" s="3" t="inlineStr">
@@ -33937,7 +33937,7 @@
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F001-W139</t>
+          <t>1G-GZRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="L300" s="2" t="inlineStr">
@@ -34053,7 +34053,7 @@
       </c>
       <c r="K301" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F002-W140</t>
+          <t>1G-GZRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="L301" s="3" t="inlineStr">
@@ -34169,7 +34169,7 @@
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F003-W141</t>
+          <t>1G-GZRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="L302" s="2" t="inlineStr">
@@ -34285,7 +34285,7 @@
       </c>
       <c r="K303" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F004-W142</t>
+          <t>1G-GZRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="L303" s="3" t="inlineStr">
@@ -34401,7 +34401,7 @@
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F005-W143</t>
+          <t>1G-GZRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="L304" s="2" t="inlineStr">
@@ -34517,7 +34517,7 @@
       </c>
       <c r="K305" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F006-W144</t>
+          <t>1G-GZRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="L305" s="3" t="inlineStr">
@@ -34633,7 +34633,7 @@
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F007-W145</t>
+          <t>1G-GZRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="L306" s="2" t="inlineStr">
@@ -34749,7 +34749,7 @@
       </c>
       <c r="K307" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F001-W146</t>
+          <t>1G-GZRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="L307" s="3" t="inlineStr">
@@ -34865,7 +34865,7 @@
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F002-W147</t>
+          <t>1G-GZRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="L308" s="2" t="inlineStr">
@@ -34981,7 +34981,7 @@
       </c>
       <c r="K309" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F003-W148</t>
+          <t>1G-GZRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="L309" s="3" t="inlineStr">
@@ -35097,7 +35097,7 @@
       </c>
       <c r="K310" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F004-W149</t>
+          <t>1G-GZRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="L310" s="2" t="inlineStr">
@@ -35213,7 +35213,7 @@
       </c>
       <c r="K311" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F005-W150</t>
+          <t>1G-GZRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="L311" s="3" t="inlineStr">
@@ -35329,7 +35329,7 @@
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F006-W151</t>
+          <t>1G-GZRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="L312" s="2" t="inlineStr">
@@ -35445,7 +35445,7 @@
       </c>
       <c r="K313" s="3" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F007-W152</t>
+          <t>1G-GZRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="L313" s="3" t="inlineStr">
@@ -35561,7 +35561,7 @@
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F001-W001</t>
+          <t>2G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="L314" s="2" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="K315" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F002-W002</t>
+          <t>2G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="L315" s="3" t="inlineStr">
@@ -35785,7 +35785,7 @@
       </c>
       <c r="K316" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F003-W003</t>
+          <t>2G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="L316" s="2" t="inlineStr">
@@ -35897,7 +35897,7 @@
       </c>
       <c r="K317" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F004-W004</t>
+          <t>2G-GGRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="L317" s="3" t="inlineStr">
@@ -36009,7 +36009,7 @@
       </c>
       <c r="K318" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F005-W005</t>
+          <t>2G-GGRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="L318" s="2" t="inlineStr">
@@ -36121,7 +36121,7 @@
       </c>
       <c r="K319" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F006-W006</t>
+          <t>2G-GGRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="L319" s="3" t="inlineStr">
@@ -36233,7 +36233,7 @@
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F007-W007</t>
+          <t>2G-GGRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="L320" s="2" t="inlineStr">
@@ -36345,7 +36345,7 @@
       </c>
       <c r="K321" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F008-W008</t>
+          <t>2G-GGRQ-GQ-L001-F008-W</t>
         </is>
       </c>
       <c r="L321" s="3" t="inlineStr">
@@ -36457,7 +36457,7 @@
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F009-W009</t>
+          <t>2G-GGRQ-GQ-L001-F009-W</t>
         </is>
       </c>
       <c r="L322" s="2" t="inlineStr">
@@ -36569,7 +36569,7 @@
       </c>
       <c r="K323" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F010-W010</t>
+          <t>2G-GGRQ-GQ-L001-F010-W</t>
         </is>
       </c>
       <c r="L323" s="3" t="inlineStr">
@@ -36681,7 +36681,7 @@
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F011-W011</t>
+          <t>2G-GGRQ-GQ-L001-F011-W</t>
         </is>
       </c>
       <c r="L324" s="2" t="inlineStr">
@@ -36793,7 +36793,7 @@
       </c>
       <c r="K325" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F012-W012</t>
+          <t>2G-GGRQ-GQ-L001-F012-W</t>
         </is>
       </c>
       <c r="L325" s="3" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="K326" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F001-W013</t>
+          <t>2G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="L326" s="2" t="inlineStr">
@@ -37017,7 +37017,7 @@
       </c>
       <c r="K327" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F002-W014</t>
+          <t>2G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="L327" s="3" t="inlineStr">
@@ -37129,7 +37129,7 @@
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F003-W015</t>
+          <t>2G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="L328" s="2" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="K329" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F004-W016</t>
+          <t>2G-GGRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="L329" s="3" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="K330" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F005-W017</t>
+          <t>2G-GGRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="L330" s="2" t="inlineStr">
@@ -37465,7 +37465,7 @@
       </c>
       <c r="K331" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F006-W018</t>
+          <t>2G-GGRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="L331" s="3" t="inlineStr">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F007-W019</t>
+          <t>2G-GGRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="L332" s="2" t="inlineStr">
@@ -37689,7 +37689,7 @@
       </c>
       <c r="K333" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F008-W020</t>
+          <t>2G-GGRQ-GQ-L003-F008-W</t>
         </is>
       </c>
       <c r="L333" s="3" t="inlineStr">
@@ -37801,7 +37801,7 @@
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F009-W021</t>
+          <t>2G-GGRQ-GQ-L003-F009-W</t>
         </is>
       </c>
       <c r="L334" s="2" t="inlineStr">
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K335" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F010-W022</t>
+          <t>2G-GGRQ-GQ-L003-F010-W</t>
         </is>
       </c>
       <c r="L335" s="3" t="inlineStr">
@@ -38025,7 +38025,7 @@
       </c>
       <c r="K336" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F011-W023</t>
+          <t>2G-GGRQ-GQ-L003-F011-W</t>
         </is>
       </c>
       <c r="L336" s="2" t="inlineStr">
@@ -38137,7 +38137,7 @@
       </c>
       <c r="K337" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F012-W024</t>
+          <t>2G-GGRQ-GQ-L003-F012-W</t>
         </is>
       </c>
       <c r="L337" s="3" t="inlineStr">
@@ -38249,7 +38249,7 @@
       </c>
       <c r="K338" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F001-W025</t>
+          <t>2G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="L338" s="2" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="K339" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F002-W026</t>
+          <t>2G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="L339" s="3" t="inlineStr">
@@ -38473,7 +38473,7 @@
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F003-W027</t>
+          <t>2G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="L340" s="2" t="inlineStr">
@@ -38585,7 +38585,7 @@
       </c>
       <c r="K341" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F004-W028</t>
+          <t>2G-GGRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="L341" s="3" t="inlineStr">
@@ -38697,7 +38697,7 @@
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F005-W029</t>
+          <t>2G-GGRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="L342" s="2" t="inlineStr">
@@ -38809,7 +38809,7 @@
       </c>
       <c r="K343" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F006-W030</t>
+          <t>2G-GGRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="L343" s="3" t="inlineStr">
@@ -38921,7 +38921,7 @@
       </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F007-W031</t>
+          <t>2G-GGRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="L344" s="2" t="inlineStr">
@@ -39033,7 +39033,7 @@
       </c>
       <c r="K345" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F008-W032</t>
+          <t>2G-GGRQ-GQ-L005-F008-W</t>
         </is>
       </c>
       <c r="L345" s="3" t="inlineStr">
@@ -39145,7 +39145,7 @@
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F009-W033</t>
+          <t>2G-GGRQ-GQ-L005-F009-W</t>
         </is>
       </c>
       <c r="L346" s="2" t="inlineStr">
@@ -39257,7 +39257,7 @@
       </c>
       <c r="K347" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F010-W034</t>
+          <t>2G-GGRQ-GQ-L005-F010-W</t>
         </is>
       </c>
       <c r="L347" s="3" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F011-W035</t>
+          <t>2G-GGRQ-GQ-L005-F011-W</t>
         </is>
       </c>
       <c r="L348" s="2" t="inlineStr">
@@ -39481,7 +39481,7 @@
       </c>
       <c r="K349" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F012-W036</t>
+          <t>2G-GGRQ-GQ-L005-F012-W</t>
         </is>
       </c>
       <c r="L349" s="3" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="K350" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F001-W037</t>
+          <t>2G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="L350" s="2" t="inlineStr">
@@ -39705,7 +39705,7 @@
       </c>
       <c r="K351" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F002-W038</t>
+          <t>2G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="L351" s="3" t="inlineStr">
@@ -39817,7 +39817,7 @@
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F003-W039</t>
+          <t>2G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="L352" s="2" t="inlineStr">
@@ -39929,7 +39929,7 @@
       </c>
       <c r="K353" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F004-W040</t>
+          <t>2G-GGRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="L353" s="3" t="inlineStr">
@@ -40041,7 +40041,7 @@
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F005-W041</t>
+          <t>2G-GGRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="L354" s="2" t="inlineStr">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="K355" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F006-W042</t>
+          <t>2G-GGRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="L355" s="3" t="inlineStr">
@@ -40265,7 +40265,7 @@
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F007-W043</t>
+          <t>2G-GGRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="L356" s="2" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="K357" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F008-W044</t>
+          <t>2G-GGRQ-GQ-L007-F008-W</t>
         </is>
       </c>
       <c r="L357" s="3" t="inlineStr">
@@ -40489,7 +40489,7 @@
       </c>
       <c r="K358" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F009-W045</t>
+          <t>2G-GGRQ-GQ-L007-F009-W</t>
         </is>
       </c>
       <c r="L358" s="2" t="inlineStr">
@@ -40601,7 +40601,7 @@
       </c>
       <c r="K359" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F010-W046</t>
+          <t>2G-GGRQ-GQ-L007-F010-W</t>
         </is>
       </c>
       <c r="L359" s="3" t="inlineStr">
@@ -40713,7 +40713,7 @@
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F011-W047</t>
+          <t>2G-GGRQ-GQ-L007-F011-W</t>
         </is>
       </c>
       <c r="L360" s="2" t="inlineStr">
@@ -40825,7 +40825,7 @@
       </c>
       <c r="K361" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F012-W048</t>
+          <t>2G-GGRQ-GQ-L007-F012-W</t>
         </is>
       </c>
       <c r="L361" s="3" t="inlineStr">
@@ -40937,7 +40937,7 @@
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F001-W049</t>
+          <t>2G-GGRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="L362" s="2" t="inlineStr">
@@ -41049,7 +41049,7 @@
       </c>
       <c r="K363" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F002-W050</t>
+          <t>2G-GGRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="L363" s="3" t="inlineStr">
@@ -41161,7 +41161,7 @@
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F003-W051</t>
+          <t>2G-GGRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="L364" s="2" t="inlineStr">
@@ -41273,7 +41273,7 @@
       </c>
       <c r="K365" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F004-W052</t>
+          <t>2G-GGRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="L365" s="3" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F005-W053</t>
+          <t>2G-GGRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="L366" s="2" t="inlineStr">
@@ -41497,7 +41497,7 @@
       </c>
       <c r="K367" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F006-W054</t>
+          <t>2G-GGRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="L367" s="3" t="inlineStr">
@@ -41609,7 +41609,7 @@
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F007-W055</t>
+          <t>2G-GGRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="L368" s="2" t="inlineStr">
@@ -41721,7 +41721,7 @@
       </c>
       <c r="K369" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F008-W056</t>
+          <t>2G-GGRQ-GQ-R001-F008-W</t>
         </is>
       </c>
       <c r="L369" s="3" t="inlineStr">
@@ -41833,7 +41833,7 @@
       </c>
       <c r="K370" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F009-W057</t>
+          <t>2G-GGRQ-GQ-R001-F009-W</t>
         </is>
       </c>
       <c r="L370" s="2" t="inlineStr">
@@ -41945,7 +41945,7 @@
       </c>
       <c r="K371" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F010-W058</t>
+          <t>2G-GGRQ-GQ-R001-F010-W</t>
         </is>
       </c>
       <c r="L371" s="3" t="inlineStr">
@@ -42057,7 +42057,7 @@
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F011-W059</t>
+          <t>2G-GGRQ-GQ-R001-F011-W</t>
         </is>
       </c>
       <c r="L372" s="2" t="inlineStr">
@@ -42169,7 +42169,7 @@
       </c>
       <c r="K373" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F012-W060</t>
+          <t>2G-GGRQ-GQ-R001-F012-W</t>
         </is>
       </c>
       <c r="L373" s="3" t="inlineStr">
@@ -42281,7 +42281,7 @@
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F001-W061</t>
+          <t>2G-GGRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="L374" s="2" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="K375" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F002-W062</t>
+          <t>2G-GGRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="L375" s="3" t="inlineStr">
@@ -42505,7 +42505,7 @@
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F003-W063</t>
+          <t>2G-GGRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="L376" s="2" t="inlineStr">
@@ -42617,7 +42617,7 @@
       </c>
       <c r="K377" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F004-W064</t>
+          <t>2G-GGRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="L377" s="3" t="inlineStr">
@@ -42729,7 +42729,7 @@
       </c>
       <c r="K378" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F005-W065</t>
+          <t>2G-GGRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="L378" s="2" t="inlineStr">
@@ -42841,7 +42841,7 @@
       </c>
       <c r="K379" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F006-W066</t>
+          <t>2G-GGRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="L379" s="3" t="inlineStr">
@@ -42953,7 +42953,7 @@
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F007-W067</t>
+          <t>2G-GGRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="L380" s="2" t="inlineStr">
@@ -43065,7 +43065,7 @@
       </c>
       <c r="K381" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F008-W068</t>
+          <t>2G-GGRQ-GQ-R003-F008-W</t>
         </is>
       </c>
       <c r="L381" s="3" t="inlineStr">
@@ -43177,7 +43177,7 @@
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F009-W069</t>
+          <t>2G-GGRQ-GQ-R003-F009-W</t>
         </is>
       </c>
       <c r="L382" s="2" t="inlineStr">
@@ -43289,7 +43289,7 @@
       </c>
       <c r="K383" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F010-W070</t>
+          <t>2G-GGRQ-GQ-R003-F010-W</t>
         </is>
       </c>
       <c r="L383" s="3" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="K384" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F011-W071</t>
+          <t>2G-GGRQ-GQ-R003-F011-W</t>
         </is>
       </c>
       <c r="L384" s="2" t="inlineStr">
@@ -43513,7 +43513,7 @@
       </c>
       <c r="K385" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F012-W072</t>
+          <t>2G-GGRQ-GQ-R003-F012-W</t>
         </is>
       </c>
       <c r="L385" s="3" t="inlineStr">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="K386" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F001-W073</t>
+          <t>2G-GGRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="L386" s="2" t="inlineStr">
@@ -43737,7 +43737,7 @@
       </c>
       <c r="K387" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F002-W074</t>
+          <t>2G-GGRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="L387" s="3" t="inlineStr">
@@ -43849,7 +43849,7 @@
       </c>
       <c r="K388" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F003-W075</t>
+          <t>2G-GGRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="L388" s="2" t="inlineStr">
@@ -43961,7 +43961,7 @@
       </c>
       <c r="K389" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F004-W076</t>
+          <t>2G-GGRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="L389" s="3" t="inlineStr">
@@ -44073,7 +44073,7 @@
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F005-W077</t>
+          <t>2G-GGRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="L390" s="2" t="inlineStr">
@@ -44185,7 +44185,7 @@
       </c>
       <c r="K391" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F006-W078</t>
+          <t>2G-GGRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="L391" s="3" t="inlineStr">
@@ -44297,7 +44297,7 @@
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F007-W079</t>
+          <t>2G-GGRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="L392" s="2" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="K393" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F008-W080</t>
+          <t>2G-GGRQ-GQ-R005-F008-W</t>
         </is>
       </c>
       <c r="L393" s="3" t="inlineStr">
@@ -44521,7 +44521,7 @@
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F009-W081</t>
+          <t>2G-GGRQ-GQ-R005-F009-W</t>
         </is>
       </c>
       <c r="L394" s="2" t="inlineStr">
@@ -44633,7 +44633,7 @@
       </c>
       <c r="K395" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F010-W082</t>
+          <t>2G-GGRQ-GQ-R005-F010-W</t>
         </is>
       </c>
       <c r="L395" s="3" t="inlineStr">
@@ -44745,7 +44745,7 @@
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F011-W083</t>
+          <t>2G-GGRQ-GQ-R005-F011-W</t>
         </is>
       </c>
       <c r="L396" s="2" t="inlineStr">
@@ -44857,7 +44857,7 @@
       </c>
       <c r="K397" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F012-W084</t>
+          <t>2G-GGRQ-GQ-R005-F012-W</t>
         </is>
       </c>
       <c r="L397" s="3" t="inlineStr">
@@ -44969,7 +44969,7 @@
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F001-W085</t>
+          <t>2G-GGRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="L398" s="2" t="inlineStr">
@@ -45081,7 +45081,7 @@
       </c>
       <c r="K399" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F002-W086</t>
+          <t>2G-GGRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="L399" s="3" t="inlineStr">
@@ -45193,7 +45193,7 @@
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F003-W087</t>
+          <t>2G-GGRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="L400" s="2" t="inlineStr">
@@ -45305,7 +45305,7 @@
       </c>
       <c r="K401" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F004-W088</t>
+          <t>2G-GGRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="L401" s="3" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="K402" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F005-W089</t>
+          <t>2G-GGRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="L402" s="2" t="inlineStr">
@@ -45529,7 +45529,7 @@
       </c>
       <c r="K403" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F006-W090</t>
+          <t>2G-GGRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="L403" s="3" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="K404" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F007-W091</t>
+          <t>2G-GGRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="L404" s="2" t="inlineStr">
@@ -45753,7 +45753,7 @@
       </c>
       <c r="K405" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F008-W092</t>
+          <t>2G-GGRQ-GQ-R007-F008-W</t>
         </is>
       </c>
       <c r="L405" s="3" t="inlineStr">
@@ -45865,7 +45865,7 @@
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F009-W093</t>
+          <t>2G-GGRQ-GQ-R007-F009-W</t>
         </is>
       </c>
       <c r="L406" s="2" t="inlineStr">
@@ -45977,7 +45977,7 @@
       </c>
       <c r="K407" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F010-W094</t>
+          <t>2G-GGRQ-GQ-R007-F010-W</t>
         </is>
       </c>
       <c r="L407" s="3" t="inlineStr">
@@ -46089,7 +46089,7 @@
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F011-W095</t>
+          <t>2G-GGRQ-GQ-R007-F011-W</t>
         </is>
       </c>
       <c r="L408" s="2" t="inlineStr">
@@ -46201,7 +46201,7 @@
       </c>
       <c r="K409" s="3" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F012-W096</t>
+          <t>2G-GGRQ-GQ-R007-F012-W</t>
         </is>
       </c>
       <c r="L409" s="3" t="inlineStr">
@@ -46313,7 +46313,7 @@
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F001-W097</t>
+          <t>2G-GZRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="L410" s="2" t="inlineStr">
@@ -46429,7 +46429,7 @@
       </c>
       <c r="K411" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F002-W098</t>
+          <t>2G-GZRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="L411" s="3" t="inlineStr">
@@ -46545,7 +46545,7 @@
       </c>
       <c r="K412" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F003-W099</t>
+          <t>2G-GZRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="L412" s="2" t="inlineStr">
@@ -46661,7 +46661,7 @@
       </c>
       <c r="K413" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F004-W100</t>
+          <t>2G-GZRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="L413" s="3" t="inlineStr">
@@ -46777,7 +46777,7 @@
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F005-W101</t>
+          <t>2G-GZRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="L414" s="2" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="K415" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F006-W102</t>
+          <t>2G-GZRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="L415" s="3" t="inlineStr">
@@ -47009,7 +47009,7 @@
       </c>
       <c r="K416" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F007-W103</t>
+          <t>2G-GZRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="L416" s="2" t="inlineStr">
@@ -47125,7 +47125,7 @@
       </c>
       <c r="K417" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F001-W104</t>
+          <t>2G-GZRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="L417" s="3" t="inlineStr">
@@ -47241,7 +47241,7 @@
       </c>
       <c r="K418" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F002-W105</t>
+          <t>2G-GZRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="L418" s="2" t="inlineStr">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="K419" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F003-W106</t>
+          <t>2G-GZRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="L419" s="3" t="inlineStr">
@@ -47473,7 +47473,7 @@
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F004-W107</t>
+          <t>2G-GZRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="L420" s="2" t="inlineStr">
@@ -47589,7 +47589,7 @@
       </c>
       <c r="K421" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F005-W108</t>
+          <t>2G-GZRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="L421" s="3" t="inlineStr">
@@ -47705,7 +47705,7 @@
       </c>
       <c r="K422" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F006-W109</t>
+          <t>2G-GZRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="L422" s="2" t="inlineStr">
@@ -47821,7 +47821,7 @@
       </c>
       <c r="K423" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F007-W110</t>
+          <t>2G-GZRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="L423" s="3" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="K424" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F001-W111</t>
+          <t>2G-GZRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="L424" s="2" t="inlineStr">
@@ -48053,7 +48053,7 @@
       </c>
       <c r="K425" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F002-W112</t>
+          <t>2G-GZRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="L425" s="3" t="inlineStr">
@@ -48169,7 +48169,7 @@
       </c>
       <c r="K426" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F003-W113</t>
+          <t>2G-GZRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="L426" s="2" t="inlineStr">
@@ -48285,7 +48285,7 @@
       </c>
       <c r="K427" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F004-W114</t>
+          <t>2G-GZRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="L427" s="3" t="inlineStr">
@@ -48401,7 +48401,7 @@
       </c>
       <c r="K428" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F005-W115</t>
+          <t>2G-GZRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="L428" s="2" t="inlineStr">
@@ -48517,7 +48517,7 @@
       </c>
       <c r="K429" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F006-W116</t>
+          <t>2G-GZRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="L429" s="3" t="inlineStr">
@@ -48633,7 +48633,7 @@
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F007-W117</t>
+          <t>2G-GZRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="L430" s="2" t="inlineStr">
@@ -48749,7 +48749,7 @@
       </c>
       <c r="K431" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F001-W118</t>
+          <t>2G-GZRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="L431" s="3" t="inlineStr">
@@ -48865,7 +48865,7 @@
       </c>
       <c r="K432" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F002-W119</t>
+          <t>2G-GZRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="L432" s="2" t="inlineStr">
@@ -48981,7 +48981,7 @@
       </c>
       <c r="K433" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F003-W120</t>
+          <t>2G-GZRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="L433" s="3" t="inlineStr">
@@ -49097,7 +49097,7 @@
       </c>
       <c r="K434" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F004-W121</t>
+          <t>2G-GZRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="L434" s="2" t="inlineStr">
@@ -49213,7 +49213,7 @@
       </c>
       <c r="K435" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F005-W122</t>
+          <t>2G-GZRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="L435" s="3" t="inlineStr">
@@ -49329,7 +49329,7 @@
       </c>
       <c r="K436" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F006-W123</t>
+          <t>2G-GZRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="L436" s="2" t="inlineStr">
@@ -49445,7 +49445,7 @@
       </c>
       <c r="K437" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F007-W124</t>
+          <t>2G-GZRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="L437" s="3" t="inlineStr">
@@ -49561,7 +49561,7 @@
       </c>
       <c r="K438" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F001-W125</t>
+          <t>2G-GZRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="L438" s="2" t="inlineStr">
@@ -49677,7 +49677,7 @@
       </c>
       <c r="K439" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F002-W126</t>
+          <t>2G-GZRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="L439" s="3" t="inlineStr">
@@ -49793,7 +49793,7 @@
       </c>
       <c r="K440" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F003-W127</t>
+          <t>2G-GZRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="L440" s="2" t="inlineStr">
@@ -49909,7 +49909,7 @@
       </c>
       <c r="K441" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F004-W128</t>
+          <t>2G-GZRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="L441" s="3" t="inlineStr">
@@ -50025,7 +50025,7 @@
       </c>
       <c r="K442" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F005-W129</t>
+          <t>2G-GZRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="L442" s="2" t="inlineStr">
@@ -50141,7 +50141,7 @@
       </c>
       <c r="K443" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F006-W130</t>
+          <t>2G-GZRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="L443" s="3" t="inlineStr">
@@ -50257,7 +50257,7 @@
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F007-W131</t>
+          <t>2G-GZRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="L444" s="2" t="inlineStr">
@@ -50373,7 +50373,7 @@
       </c>
       <c r="K445" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F001-W132</t>
+          <t>2G-GZRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="L445" s="3" t="inlineStr">
@@ -50489,7 +50489,7 @@
       </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F002-W133</t>
+          <t>2G-GZRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="L446" s="2" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="K447" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F003-W134</t>
+          <t>2G-GZRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="L447" s="3" t="inlineStr">
@@ -50721,7 +50721,7 @@
       </c>
       <c r="K448" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F004-W135</t>
+          <t>2G-GZRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="L448" s="2" t="inlineStr">
@@ -50837,7 +50837,7 @@
       </c>
       <c r="K449" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F005-W136</t>
+          <t>2G-GZRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="L449" s="3" t="inlineStr">
@@ -50953,7 +50953,7 @@
       </c>
       <c r="K450" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F006-W137</t>
+          <t>2G-GZRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="L450" s="2" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="K451" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F007-W138</t>
+          <t>2G-GZRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="L451" s="3" t="inlineStr">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="K452" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F001-W139</t>
+          <t>2G-GZRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="L452" s="2" t="inlineStr">
@@ -51301,7 +51301,7 @@
       </c>
       <c r="K453" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F002-W140</t>
+          <t>2G-GZRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="L453" s="3" t="inlineStr">
@@ -51417,7 +51417,7 @@
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F003-W141</t>
+          <t>2G-GZRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="L454" s="2" t="inlineStr">
@@ -51533,7 +51533,7 @@
       </c>
       <c r="K455" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F004-W142</t>
+          <t>2G-GZRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="L455" s="3" t="inlineStr">
@@ -51649,7 +51649,7 @@
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F005-W143</t>
+          <t>2G-GZRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="L456" s="2" t="inlineStr">
@@ -51765,7 +51765,7 @@
       </c>
       <c r="K457" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F006-W144</t>
+          <t>2G-GZRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="L457" s="3" t="inlineStr">
@@ -51881,7 +51881,7 @@
       </c>
       <c r="K458" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F007-W145</t>
+          <t>2G-GZRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="L458" s="2" t="inlineStr">
@@ -51997,7 +51997,7 @@
       </c>
       <c r="K459" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F001-W146</t>
+          <t>2G-GZRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="L459" s="3" t="inlineStr">
@@ -52113,7 +52113,7 @@
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F002-W147</t>
+          <t>2G-GZRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="L460" s="2" t="inlineStr">
@@ -52229,7 +52229,7 @@
       </c>
       <c r="K461" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F003-W148</t>
+          <t>2G-GZRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="L461" s="3" t="inlineStr">
@@ -52345,7 +52345,7 @@
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F004-W149</t>
+          <t>2G-GZRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="L462" s="2" t="inlineStr">
@@ -52461,7 +52461,7 @@
       </c>
       <c r="K463" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F005-W150</t>
+          <t>2G-GZRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="L463" s="3" t="inlineStr">
@@ -52577,7 +52577,7 @@
       </c>
       <c r="K464" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F006-W151</t>
+          <t>2G-GZRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="L464" s="2" t="inlineStr">
@@ -52693,7 +52693,7 @@
       </c>
       <c r="K465" s="3" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F007-W152</t>
+          <t>2G-GZRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="L465" s="3" t="inlineStr">
@@ -53263,7 +53263,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W064</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -53371,7 +53371,7 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W065</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -53479,7 +53479,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F002-W066</t>
+          <t>1G-GGRQ-GQ-L002-F002-W</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -53587,7 +53587,7 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F003-W067</t>
+          <t>1G-GGRQ-GQ-L002-F003-W</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -53695,7 +53695,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W068</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -53803,7 +53803,7 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W069</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -53911,7 +53911,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F002-W070</t>
+          <t>1G-GGRQ-GQ-L004-F002-W</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -54019,7 +54019,7 @@
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W073</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -54127,7 +54127,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F002-W074</t>
+          <t>1G-GGRQ-GQ-L006-F002-W</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -54235,7 +54235,7 @@
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F003-W075</t>
+          <t>1G-GGRQ-GQ-L006-F003-W</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -54343,7 +54343,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W076</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -54451,7 +54451,7 @@
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W077</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -54559,7 +54559,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F002-W078</t>
+          <t>1G-GGRQ-GQ-L008-F002-W</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -54667,7 +54667,7 @@
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F003-W079</t>
+          <t>1G-GGRQ-GQ-L008-F003-W</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -54775,7 +54775,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F002-W080</t>
+          <t>1G-GGRQ-GQ-L009-F002-W</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -54883,7 +54883,7 @@
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F003-W081</t>
+          <t>1G-GGRQ-GQ-L009-F003-W</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -54991,7 +54991,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F003-W083</t>
+          <t>1G-GGRQ-GQ-L010-F003-W</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -55099,7 +55099,7 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F002-W084</t>
+          <t>1G-GGRQ-GQ-L011-F002-W</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -55207,7 +55207,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F003-W085</t>
+          <t>1G-GGRQ-GQ-L011-F003-W</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -55315,7 +55315,7 @@
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F002-W086</t>
+          <t>1G-GGRQ-GQ-L012-F002-W</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -55423,7 +55423,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F003-W087</t>
+          <t>1G-GGRQ-GQ-L012-F003-W</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -55531,7 +55531,7 @@
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F003-W089</t>
+          <t>1G-GGRQ-GQ-L013-F003-W</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -55639,7 +55639,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F002-W090</t>
+          <t>1G-GGRQ-GQ-L014-F002-W</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -55747,7 +55747,7 @@
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F003-W091</t>
+          <t>1G-GGRQ-GQ-L014-F003-W</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -55855,7 +55855,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F002-W092</t>
+          <t>1G-GGRQ-GQ-L015-F002-W</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -55963,7 +55963,7 @@
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F003-W093</t>
+          <t>1G-GGRQ-GQ-L015-F003-W</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -56071,7 +56071,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F002-W094</t>
+          <t>1G-GGRQ-GQ-L016-F002-W</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -56179,7 +56179,7 @@
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F003-W095</t>
+          <t>1G-GGRQ-GQ-L016-F003-W</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -56287,7 +56287,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F002-W096</t>
+          <t>1G-GGRQ-GQ-L017-F002-W</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -56395,7 +56395,7 @@
       <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F003-W097</t>
+          <t>1G-GGRQ-GQ-L017-F003-W</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -56503,7 +56503,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F002-W098</t>
+          <t>1G-GGRQ-GQ-L018-F002-W</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -56611,7 +56611,7 @@
       <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F003-W099</t>
+          <t>1G-GGRQ-GQ-L018-F003-W</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -56719,7 +56719,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F002-W100</t>
+          <t>1G-GGRQ-GQ-L019-F002-W</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -56827,7 +56827,7 @@
       <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F003-W101</t>
+          <t>1G-GGRQ-GQ-L019-F003-W</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -56935,7 +56935,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F002-W102</t>
+          <t>1G-GGRQ-GQ-L020-F002-W</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -57043,7 +57043,7 @@
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F003-W103</t>
+          <t>1G-GGRQ-GQ-L020-F003-W</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -57151,7 +57151,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F002-W104</t>
+          <t>1G-GGRQ-GQ-L021-F002-W</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -57259,7 +57259,7 @@
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F003-W105</t>
+          <t>1G-GGRQ-GQ-L021-F003-W</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -57367,7 +57367,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F002-W106</t>
+          <t>1G-GGRQ-GQ-L022-F002-W</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -57475,7 +57475,7 @@
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F003-W107</t>
+          <t>1G-GGRQ-GQ-L022-F003-W</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -57583,7 +57583,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F002-W108</t>
+          <t>1G-GGRQ-GQ-L023-F002-W</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -57691,7 +57691,7 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F003-W109</t>
+          <t>1G-GGRQ-GQ-L023-F003-W</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -57799,7 +57799,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F002-W110</t>
+          <t>1G-GGRQ-GQ-L024-F002-W</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -57907,7 +57907,7 @@
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F003-W111</t>
+          <t>1G-GGRQ-GQ-L024-F003-W</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -58015,7 +58015,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F003-W113</t>
+          <t>1G-GGRQ-GQ-L025-F003-W</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -58123,7 +58123,7 @@
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F002-W114</t>
+          <t>1G-GGRQ-GQ-L026-F002-W</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -58231,7 +58231,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F003-W115</t>
+          <t>1G-GGRQ-GQ-L026-F003-W</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -58339,7 +58339,7 @@
       <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F002-W116</t>
+          <t>1G-GGRQ-GQ-L027-F002-W</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -58447,7 +58447,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F003-W117</t>
+          <t>1G-GGRQ-GQ-L027-F003-W</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -58555,7 +58555,7 @@
       <c r="J51" s="3" t="inlineStr"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F002-W118</t>
+          <t>1G-GGRQ-GQ-L028-F002-W</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -58663,7 +58663,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F003-W119</t>
+          <t>1G-GGRQ-GQ-L028-F003-W</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -58771,7 +58771,7 @@
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F002-W120</t>
+          <t>1G-GGRQ-GQ-L029-F002-W</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -58879,7 +58879,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F003-W121</t>
+          <t>1G-GGRQ-GQ-L029-F003-W</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -58987,7 +58987,7 @@
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F002-W122</t>
+          <t>1G-GGRQ-GQ-L030-F002-W</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -59095,7 +59095,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F003-W123</t>
+          <t>1G-GGRQ-GQ-L030-F003-W</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -59203,7 +59203,7 @@
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F002-W124</t>
+          <t>1G-GGRQ-GQ-L031-F002-W</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -59311,7 +59311,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F003-W125</t>
+          <t>1G-GGRQ-GQ-L031-F003-W</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -59419,7 +59419,7 @@
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F002-W126</t>
+          <t>1G-GGRQ-GQ-L032-F002-W</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -59527,7 +59527,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F003-W127</t>
+          <t>1G-GGRQ-GQ-L032-F003-W</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -59635,7 +59635,7 @@
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W128</t>
+          <t>1G-GGRQ-GQ-L001-B001-W</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
@@ -59743,7 +59743,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W129</t>
+          <t>1G-GGRQ-GQ-L002-B001-W</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -59851,7 +59851,7 @@
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W130</t>
+          <t>1G-GGRQ-GQ-L003-B001-W</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
@@ -59959,7 +59959,7 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W131</t>
+          <t>1G-GGRQ-GQ-L004-B001-W</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -60067,7 +60067,7 @@
       <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W132</t>
+          <t>1G-GGRQ-GQ-L005-B001-W</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -60175,7 +60175,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W133</t>
+          <t>1G-GGRQ-GQ-L006-B001-W</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -60283,7 +60283,7 @@
       <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W134</t>
+          <t>1G-GGRQ-GQ-L007-B001-W</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -60391,7 +60391,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W135</t>
+          <t>1G-GGRQ-GQ-L008-B001-W</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -60499,7 +60499,7 @@
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W136</t>
+          <t>1G-GGRQ-GQ-L009-B001-W</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
@@ -60607,7 +60607,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W137</t>
+          <t>1G-GGRQ-GQ-L010-B001-W</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -60715,7 +60715,7 @@
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W138</t>
+          <t>1G-GGRQ-GQ-L011-B001-W</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
@@ -60823,7 +60823,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W139</t>
+          <t>1G-GGRQ-GQ-L012-B001-W</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -60931,7 +60931,7 @@
       <c r="J73" s="3" t="inlineStr"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W140</t>
+          <t>1G-GGRQ-GQ-L013-B001-W</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
@@ -61039,7 +61039,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W141</t>
+          <t>1G-GGRQ-GQ-L014-B001-W</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -61147,7 +61147,7 @@
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W142</t>
+          <t>1G-GGRQ-GQ-L015-B001-W</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -61255,7 +61255,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W143</t>
+          <t>1G-GGRQ-GQ-L016-B001-W</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -61363,7 +61363,7 @@
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W144</t>
+          <t>1G-GGRQ-GQ-L017-B001-W</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
@@ -61471,7 +61471,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W145</t>
+          <t>1G-GGRQ-GQ-L018-B001-W</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -61579,7 +61579,7 @@
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W146</t>
+          <t>1G-GGRQ-GQ-L019-B001-W</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
@@ -61687,7 +61687,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W147</t>
+          <t>1G-GGRQ-GQ-L020-B001-W</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -61795,7 +61795,7 @@
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W148</t>
+          <t>1G-GGRQ-GQ-L021-B001-W</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
@@ -61903,7 +61903,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W149</t>
+          <t>1G-GGRQ-GQ-L022-B001-W</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -62011,7 +62011,7 @@
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W150</t>
+          <t>1G-GGRQ-GQ-L023-B001-W</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
@@ -62119,7 +62119,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W151</t>
+          <t>1G-GGRQ-GQ-L024-B001-W</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -62227,7 +62227,7 @@
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W152</t>
+          <t>1G-GGRQ-GQ-L025-B001-W</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
@@ -62335,7 +62335,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W153</t>
+          <t>1G-GGRQ-GQ-L026-B001-W</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -62443,7 +62443,7 @@
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W154</t>
+          <t>1G-GGRQ-GQ-L027-B001-W</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
@@ -62551,7 +62551,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W155</t>
+          <t>1G-GGRQ-GQ-L028-B001-W</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -62659,7 +62659,7 @@
       <c r="J89" s="3" t="inlineStr"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W156</t>
+          <t>1G-GGRQ-GQ-L029-B001-W</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
@@ -62767,7 +62767,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W157</t>
+          <t>1G-GGRQ-GQ-L030-B001-W</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -62875,7 +62875,7 @@
       <c r="J91" s="3" t="inlineStr"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W158</t>
+          <t>1G-GGRQ-GQ-L031-B001-W</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
@@ -62983,7 +62983,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W159</t>
+          <t>1G-GGRQ-GQ-L032-B001-W</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">

--- a/data-cleaning/verified/数据清洗审计.xlsx
+++ b/data-cleaning/verified/数据清洗审计.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'汇总展开追溯'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'来源行映射'!$A$1:$H$69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'来源行映射'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'问题清单'!$A$1:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'问题清单'!$A$1:$G$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'问题清单'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'语义自检'!$A$1:$C$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'语义自检'!$1:$1</definedName>
@@ -509,7 +509,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>film-records-physical-codes-v3</t>
+          <t>film-records-physical-codes-v4</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>编码=位置+Q/W字母尾，永久唯一；流水号只在溯源列；F/B几何、独立物理管总数未确认</t>
+          <t>编码=位置+Q/W字母尾，永久唯一；流水号只在溯源列；高过每屏24根及F↔B、L↔R镜像为用户确认口径</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="33.59999999999999" customWidth="1" min="17" max="17"/>
-    <col width="33.59999999999999" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
@@ -955,8 +955,16 @@
           <t>L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -969,12 +977,12 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S2" s="4" t="inlineStr">
@@ -1014,7 +1022,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F004=炉后第21弯头→304H</t>
         </is>
       </c>
     </row>
@@ -1067,8 +1075,16 @@
           <t>L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1081,12 +1097,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
@@ -1126,7 +1142,7 @@
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F005=炉后第20弯头→T91</t>
         </is>
       </c>
     </row>
@@ -1179,8 +1195,16 @@
           <t>L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1193,12 +1217,12 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S4" s="4" t="inlineStr">
@@ -1238,7 +1262,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F006=炉后第19弯头→T91</t>
         </is>
       </c>
     </row>
@@ -1291,8 +1315,16 @@
           <t>L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1305,12 +1337,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S5" s="5" t="inlineStr">
@@ -1350,7 +1382,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F007=炉后第18弯头→T91</t>
         </is>
       </c>
     </row>
@@ -1403,8 +1435,16 @@
           <t>L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1417,12 +1457,12 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
@@ -1462,7 +1502,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F008=炉后第17弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -1515,8 +1555,16 @@
           <t>L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1529,12 +1577,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
@@ -1574,7 +1622,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F009=炉后第16弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -1627,8 +1675,16 @@
           <t>L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1641,12 +1697,12 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr">
@@ -1686,7 +1742,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F010=炉后第15弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -1739,8 +1795,16 @@
           <t>L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1753,12 +1817,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr">
@@ -1798,7 +1862,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F014=炉后第11弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -1851,8 +1915,16 @@
           <t>L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1865,12 +1937,12 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr">
@@ -1910,7 +1982,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F015=炉后第10弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -1963,8 +2035,16 @@
           <t>L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -1977,12 +2057,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
@@ -2022,7 +2102,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F016=炉后第9弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -2075,8 +2155,16 @@
           <t>L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2089,12 +2177,12 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
@@ -2134,7 +2222,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F017=炉后第8弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -2187,8 +2275,16 @@
           <t>L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2201,12 +2297,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
@@ -2246,7 +2342,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F018=炉后第7弯头→T91</t>
         </is>
       </c>
     </row>
@@ -2299,8 +2395,16 @@
           <t>L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2313,12 +2417,12 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
@@ -2358,7 +2462,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F019=炉后第6弯头→T91</t>
         </is>
       </c>
     </row>
@@ -2411,8 +2515,16 @@
           <t>L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2425,12 +2537,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
@@ -2470,7 +2582,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F020=炉后第5弯头→T91</t>
         </is>
       </c>
     </row>
@@ -2523,8 +2635,16 @@
           <t>L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2537,12 +2657,12 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -2582,7 +2702,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F021=炉后第4弯头→304H</t>
         </is>
       </c>
     </row>
@@ -2635,8 +2755,16 @@
           <t>L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2649,12 +2777,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
@@ -2694,7 +2822,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F022=炉后第3弯头→304H</t>
         </is>
       </c>
     </row>
@@ -2743,8 +2871,16 @@
           <t>L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2757,12 +2893,12 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
@@ -2802,7 +2938,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F004=炉后第21弯头→304H</t>
         </is>
       </c>
     </row>
@@ -2851,8 +2987,16 @@
           <t>L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2865,12 +3009,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
@@ -2910,7 +3054,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F005=炉后第20弯头→T91</t>
         </is>
       </c>
     </row>
@@ -2959,8 +3103,16 @@
           <t>L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -2973,12 +3125,12 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
@@ -3018,7 +3170,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F006=炉后第19弯头→T91</t>
         </is>
       </c>
     </row>
@@ -3067,8 +3219,16 @@
           <t>L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3081,12 +3241,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
@@ -3126,7 +3286,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F007=炉后第18弯头→T91</t>
         </is>
       </c>
     </row>
@@ -3175,8 +3335,16 @@
           <t>L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3189,12 +3357,12 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
@@ -3234,7 +3402,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F008=炉后第17弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -3283,8 +3451,16 @@
           <t>L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3297,12 +3473,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
@@ -3342,7 +3518,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F009=炉后第16弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -3391,8 +3567,16 @@
           <t>L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3405,12 +3589,12 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -3450,7 +3634,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F010=炉后第15弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -3499,8 +3683,16 @@
           <t>L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3513,12 +3705,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
@@ -3558,7 +3750,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F014=炉后第11弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -3607,8 +3799,16 @@
           <t>L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3621,12 +3821,12 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
@@ -3666,7 +3866,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F015=炉后第10弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -3715,8 +3915,16 @@
           <t>L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3729,12 +3937,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S27" s="5" t="inlineStr">
@@ -3774,7 +3982,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F016=炉后第9弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -3823,8 +4031,16 @@
           <t>L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3837,12 +4053,12 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S28" s="4" t="inlineStr">
@@ -3882,7 +4098,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F017=炉后第8弯头→12CrMoVG</t>
         </is>
       </c>
     </row>
@@ -3931,8 +4147,16 @@
           <t>L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -3945,12 +4169,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S29" s="5" t="inlineStr">
@@ -3990,7 +4214,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F018=炉后第7弯头→T91</t>
         </is>
       </c>
     </row>
@@ -4039,8 +4263,16 @@
           <t>L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -4053,12 +4285,12 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr">
@@ -4098,7 +4330,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F019=炉后第6弯头→T91</t>
         </is>
       </c>
     </row>
@@ -4147,8 +4379,16 @@
           <t>L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -4161,12 +4401,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S31" s="5" t="inlineStr">
@@ -4206,7 +4446,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F020=炉后第5弯头→T91</t>
         </is>
       </c>
     </row>
@@ -4255,8 +4495,16 @@
           <t>L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -4269,12 +4517,12 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S32" s="4" t="inlineStr">
@@ -4314,7 +4562,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F021=炉后第4弯头→304H</t>
         </is>
       </c>
     </row>
@@ -4363,8 +4611,16 @@
           <t>L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
           <t>Φ54×7.5 / Φ51×8 / Φ51×9</t>
@@ -4377,12 +4633,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按区带材质与源行规格-材质配对</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>多值或未提供，待确认；未按W流水号分配</t>
+          <t>按用户确认每屏24根与备注弯头区带映射（炉后计数↔F管位）</t>
         </is>
       </c>
       <c r="S33" s="5" t="inlineStr">
@@ -4422,7 +4678,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>材质按管位区带映射：F022=炉后第3弯头→304H</t>
         </is>
       </c>
     </row>
@@ -7988,7 +8244,7 @@
       <c r="Y66" s="2" t="inlineStr"/>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8352,7 @@
       <c r="Y67" s="3" t="inlineStr"/>
       <c r="Z67" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8460,7 @@
       <c r="Y68" s="2" t="inlineStr"/>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8568,7 @@
       <c r="Y69" s="3" t="inlineStr"/>
       <c r="Z69" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8676,7 @@
       <c r="Y70" s="2" t="inlineStr"/>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8784,7 @@
       <c r="Y71" s="3" t="inlineStr"/>
       <c r="Z71" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8892,7 @@
       <c r="Y72" s="2" t="inlineStr"/>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8748,7 +9004,7 @@
       <c r="Y73" s="3" t="inlineStr"/>
       <c r="Z73" s="3" t="inlineStr">
         <is>
-          <t>规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8860,7 +9116,7 @@
       <c r="Y74" s="2" t="inlineStr"/>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -8968,7 +9224,7 @@
       <c r="Y75" s="3" t="inlineStr"/>
       <c r="Z75" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9332,7 @@
       <c r="Y76" s="2" t="inlineStr"/>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9440,7 @@
       <c r="Y77" s="3" t="inlineStr"/>
       <c r="Z77" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9548,7 @@
       <c r="Y78" s="2" t="inlineStr"/>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9656,7 @@
       <c r="Y79" s="3" t="inlineStr"/>
       <c r="Z79" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9764,7 @@
       <c r="Y80" s="2" t="inlineStr"/>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9872,7 @@
       <c r="Y81" s="3" t="inlineStr"/>
       <c r="Z81" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9980,7 @@
       <c r="Y82" s="2" t="inlineStr"/>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9832,7 +10088,7 @@
       <c r="Y83" s="3" t="inlineStr"/>
       <c r="Z83" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -9944,7 +10200,7 @@
       <c r="Y84" s="2" t="inlineStr"/>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10308,7 @@
       <c r="Y85" s="3" t="inlineStr"/>
       <c r="Z85" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10160,7 +10416,7 @@
       <c r="Y86" s="2" t="inlineStr"/>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10524,7 @@
       <c r="Y87" s="3" t="inlineStr"/>
       <c r="Z87" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10632,7 @@
       <c r="Y88" s="2" t="inlineStr"/>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10740,7 @@
       <c r="Y89" s="3" t="inlineStr"/>
       <c r="Z89" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10852,7 @@
       <c r="Y90" s="2" t="inlineStr"/>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10960,7 @@
       <c r="Y91" s="3" t="inlineStr"/>
       <c r="Z91" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10812,7 +11068,7 @@
       <c r="Y92" s="2" t="inlineStr"/>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -10920,7 +11176,7 @@
       <c r="Y93" s="3" t="inlineStr"/>
       <c r="Z93" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11284,7 @@
       <c r="Y94" s="2" t="inlineStr"/>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11392,7 @@
       <c r="Y95" s="3" t="inlineStr"/>
       <c r="Z95" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11500,7 @@
       <c r="Y96" s="2" t="inlineStr"/>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11608,7 @@
       <c r="Y97" s="3" t="inlineStr"/>
       <c r="Z97" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11716,7 @@
       <c r="Y98" s="2" t="inlineStr"/>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11824,7 @@
       <c r="Y99" s="3" t="inlineStr"/>
       <c r="Z99" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11932,7 @@
       <c r="Y100" s="2" t="inlineStr"/>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11784,7 +12040,7 @@
       <c r="Y101" s="3" t="inlineStr"/>
       <c r="Z101" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -11892,7 +12148,7 @@
       <c r="Y102" s="2" t="inlineStr"/>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12256,7 @@
       <c r="Y103" s="3" t="inlineStr"/>
       <c r="Z103" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12364,7 @@
       <c r="Y104" s="2" t="inlineStr"/>
       <c r="Z104" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12472,7 @@
       <c r="Y105" s="3" t="inlineStr"/>
       <c r="Z105" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12580,7 @@
       <c r="Y106" s="2" t="inlineStr"/>
       <c r="Z106" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12688,7 @@
       <c r="Y107" s="3" t="inlineStr"/>
       <c r="Z107" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12796,7 @@
       <c r="Y108" s="2" t="inlineStr"/>
       <c r="Z108" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12904,7 @@
       <c r="Y109" s="3" t="inlineStr"/>
       <c r="Z109" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12756,7 +13012,7 @@
       <c r="Y110" s="2" t="inlineStr"/>
       <c r="Z110" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12864,7 +13120,7 @@
       <c r="Y111" s="3" t="inlineStr"/>
       <c r="Z111" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -12972,7 +13228,7 @@
       <c r="Y112" s="2" t="inlineStr"/>
       <c r="Z112" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13336,7 @@
       <c r="Y113" s="3" t="inlineStr"/>
       <c r="Z113" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13448,7 @@
       <c r="Y114" s="2" t="inlineStr"/>
       <c r="Z114" s="2" t="inlineStr">
         <is>
-          <t>规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13556,7 @@
       <c r="Y115" s="3" t="inlineStr"/>
       <c r="Z115" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13408,7 +13664,7 @@
       <c r="Y116" s="2" t="inlineStr"/>
       <c r="Z116" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13516,7 +13772,7 @@
       <c r="Y117" s="3" t="inlineStr"/>
       <c r="Z117" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13624,7 +13880,7 @@
       <c r="Y118" s="2" t="inlineStr"/>
       <c r="Z118" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13988,7 @@
       <c r="Y119" s="3" t="inlineStr"/>
       <c r="Z119" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13840,7 +14096,7 @@
       <c r="Y120" s="2" t="inlineStr"/>
       <c r="Z120" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -13948,7 +14204,7 @@
       <c r="Y121" s="3" t="inlineStr"/>
       <c r="Z121" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14312,7 @@
       <c r="Y122" s="2" t="inlineStr"/>
       <c r="Z122" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14164,7 +14420,7 @@
       <c r="Y123" s="3" t="inlineStr"/>
       <c r="Z123" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14528,7 @@
       <c r="Y124" s="2" t="inlineStr"/>
       <c r="Z124" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14636,7 @@
       <c r="Y125" s="3" t="inlineStr"/>
       <c r="Z125" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14744,7 @@
       <c r="Y126" s="2" t="inlineStr"/>
       <c r="Z126" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14852,7 @@
       <c r="Y127" s="3" t="inlineStr"/>
       <c r="Z127" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14704,7 +14960,7 @@
       <c r="Y128" s="2" t="inlineStr"/>
       <c r="Z128" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14812,7 +15068,7 @@
       <c r="Y129" s="3" t="inlineStr"/>
       <c r="Z129" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -14849,12 +15105,12 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W</t>
+          <t>1G-GGRQ-GQ-L001-F024-W</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>L001-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L001-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -14920,7 +15176,7 @@
       <c r="Y130" s="2" t="inlineStr"/>
       <c r="Z130" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -14957,12 +15213,12 @@
       <c r="J131" s="3" t="inlineStr"/>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W</t>
+          <t>1G-GGRQ-GQ-L002-F024-W</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>L002-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L002-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
@@ -15028,7 +15284,7 @@
       <c r="Y131" s="3" t="inlineStr"/>
       <c r="Z131" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15065,12 +15321,12 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W</t>
+          <t>1G-GGRQ-GQ-L003-F024-W</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>L003-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L003-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -15136,7 +15392,7 @@
       <c r="Y132" s="2" t="inlineStr"/>
       <c r="Z132" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15173,12 +15429,12 @@
       <c r="J133" s="3" t="inlineStr"/>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W</t>
+          <t>1G-GGRQ-GQ-L004-F024-W</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>L004-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L004-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M133" s="3" t="inlineStr">
@@ -15244,7 +15500,7 @@
       <c r="Y133" s="3" t="inlineStr"/>
       <c r="Z133" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15281,12 +15537,12 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W</t>
+          <t>1G-GGRQ-GQ-L005-F024-W</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>L005-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L005-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
@@ -15352,7 +15608,7 @@
       <c r="Y134" s="2" t="inlineStr"/>
       <c r="Z134" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15389,12 +15645,12 @@
       <c r="J135" s="3" t="inlineStr"/>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W</t>
+          <t>1G-GGRQ-GQ-L006-F024-W</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>L006-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L006-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M135" s="3" t="inlineStr">
@@ -15460,7 +15716,7 @@
       <c r="Y135" s="3" t="inlineStr"/>
       <c r="Z135" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15497,12 +15753,12 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W</t>
+          <t>1G-GGRQ-GQ-L007-F024-W</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>L007-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L007-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -15568,7 +15824,7 @@
       <c r="Y136" s="2" t="inlineStr"/>
       <c r="Z136" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15605,12 +15861,12 @@
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W</t>
+          <t>1G-GGRQ-GQ-L008-F024-W</t>
         </is>
       </c>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>L008-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L008-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M137" s="3" t="inlineStr">
@@ -15676,7 +15932,7 @@
       <c r="Y137" s="3" t="inlineStr"/>
       <c r="Z137" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15713,12 +15969,12 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W</t>
+          <t>1G-GGRQ-GQ-L009-F024-W</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>L009-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L009-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -15784,7 +16040,7 @@
       <c r="Y138" s="2" t="inlineStr"/>
       <c r="Z138" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15821,12 +16077,12 @@
       <c r="J139" s="3" t="inlineStr"/>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W</t>
+          <t>1G-GGRQ-GQ-L010-F024-W</t>
         </is>
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>L010-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L010-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M139" s="3" t="inlineStr">
@@ -15892,7 +16148,7 @@
       <c r="Y139" s="3" t="inlineStr"/>
       <c r="Z139" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -15929,12 +16185,12 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W</t>
+          <t>1G-GGRQ-GQ-L011-F024-W</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>L011-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L011-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -16000,7 +16256,7 @@
       <c r="Y140" s="2" t="inlineStr"/>
       <c r="Z140" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16037,12 +16293,12 @@
       <c r="J141" s="3" t="inlineStr"/>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W</t>
+          <t>1G-GGRQ-GQ-L012-F024-W</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>L012-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L012-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M141" s="3" t="inlineStr">
@@ -16108,7 +16364,7 @@
       <c r="Y141" s="3" t="inlineStr"/>
       <c r="Z141" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16145,12 +16401,12 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W</t>
+          <t>1G-GGRQ-GQ-L013-F024-W</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>L013-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L013-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -16216,7 +16472,7 @@
       <c r="Y142" s="2" t="inlineStr"/>
       <c r="Z142" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16253,12 +16509,12 @@
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W</t>
+          <t>1G-GGRQ-GQ-L014-F024-W</t>
         </is>
       </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>L014-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L014-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M143" s="3" t="inlineStr">
@@ -16324,7 +16580,7 @@
       <c r="Y143" s="3" t="inlineStr"/>
       <c r="Z143" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16361,12 +16617,12 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W</t>
+          <t>1G-GGRQ-GQ-L015-F024-W</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>L015-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L015-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -16432,7 +16688,7 @@
       <c r="Y144" s="2" t="inlineStr"/>
       <c r="Z144" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16469,12 +16725,12 @@
       <c r="J145" s="3" t="inlineStr"/>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W</t>
+          <t>1G-GGRQ-GQ-L016-F024-W</t>
         </is>
       </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>L016-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L016-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M145" s="3" t="inlineStr">
@@ -16540,7 +16796,7 @@
       <c r="Y145" s="3" t="inlineStr"/>
       <c r="Z145" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16577,12 +16833,12 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W</t>
+          <t>1G-GGRQ-GQ-L017-F024-W</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>L017-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L017-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -16648,7 +16904,7 @@
       <c r="Y146" s="2" t="inlineStr"/>
       <c r="Z146" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16685,12 +16941,12 @@
       <c r="J147" s="3" t="inlineStr"/>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W</t>
+          <t>1G-GGRQ-GQ-L018-F024-W</t>
         </is>
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>L018-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L018-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M147" s="3" t="inlineStr">
@@ -16756,7 +17012,7 @@
       <c r="Y147" s="3" t="inlineStr"/>
       <c r="Z147" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16793,12 +17049,12 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W</t>
+          <t>1G-GGRQ-GQ-L019-F024-W</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>L019-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L019-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -16864,7 +17120,7 @@
       <c r="Y148" s="2" t="inlineStr"/>
       <c r="Z148" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -16901,12 +17157,12 @@
       <c r="J149" s="3" t="inlineStr"/>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W</t>
+          <t>1G-GGRQ-GQ-L020-F024-W</t>
         </is>
       </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
-          <t>L020-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L020-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M149" s="3" t="inlineStr">
@@ -16972,7 +17228,7 @@
       <c r="Y149" s="3" t="inlineStr"/>
       <c r="Z149" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17009,12 +17265,12 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W</t>
+          <t>1G-GGRQ-GQ-L021-F024-W</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>L021-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L021-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -17080,7 +17336,7 @@
       <c r="Y150" s="2" t="inlineStr"/>
       <c r="Z150" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17117,12 +17373,12 @@
       <c r="J151" s="3" t="inlineStr"/>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W</t>
+          <t>1G-GGRQ-GQ-L022-F024-W</t>
         </is>
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>L022-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L022-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M151" s="3" t="inlineStr">
@@ -17188,7 +17444,7 @@
       <c r="Y151" s="3" t="inlineStr"/>
       <c r="Z151" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17225,12 +17481,12 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W</t>
+          <t>1G-GGRQ-GQ-L023-F024-W</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>L023-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L023-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -17296,7 +17552,7 @@
       <c r="Y152" s="2" t="inlineStr"/>
       <c r="Z152" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17333,12 +17589,12 @@
       <c r="J153" s="3" t="inlineStr"/>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W</t>
+          <t>1G-GGRQ-GQ-L024-F024-W</t>
         </is>
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>L024-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L024-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M153" s="3" t="inlineStr">
@@ -17404,7 +17660,7 @@
       <c r="Y153" s="3" t="inlineStr"/>
       <c r="Z153" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17441,12 +17697,12 @@
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W</t>
+          <t>1G-GGRQ-GQ-L025-F024-W</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>L025-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L025-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -17512,7 +17768,7 @@
       <c r="Y154" s="2" t="inlineStr"/>
       <c r="Z154" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17549,12 +17805,12 @@
       <c r="J155" s="3" t="inlineStr"/>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W</t>
+          <t>1G-GGRQ-GQ-L026-F024-W</t>
         </is>
       </c>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>L026-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L026-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M155" s="3" t="inlineStr">
@@ -17620,7 +17876,7 @@
       <c r="Y155" s="3" t="inlineStr"/>
       <c r="Z155" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17657,12 +17913,12 @@
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W</t>
+          <t>1G-GGRQ-GQ-L027-F024-W</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>L027-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L027-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -17728,7 +17984,7 @@
       <c r="Y156" s="2" t="inlineStr"/>
       <c r="Z156" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17765,12 +18021,12 @@
       <c r="J157" s="3" t="inlineStr"/>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W</t>
+          <t>1G-GGRQ-GQ-L028-F024-W</t>
         </is>
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>L028-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L028-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M157" s="3" t="inlineStr">
@@ -17836,7 +18092,7 @@
       <c r="Y157" s="3" t="inlineStr"/>
       <c r="Z157" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17873,12 +18129,12 @@
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W</t>
+          <t>1G-GGRQ-GQ-L029-F024-W</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>L029-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L029-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -17944,7 +18200,7 @@
       <c r="Y158" s="2" t="inlineStr"/>
       <c r="Z158" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -17981,12 +18237,12 @@
       <c r="J159" s="3" t="inlineStr"/>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W</t>
+          <t>1G-GGRQ-GQ-L030-F024-W</t>
         </is>
       </c>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>L030-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L030-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M159" s="3" t="inlineStr">
@@ -18052,7 +18308,7 @@
       <c r="Y159" s="3" t="inlineStr"/>
       <c r="Z159" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -18089,12 +18345,12 @@
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W</t>
+          <t>1G-GGRQ-GQ-L031-F024-W</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>L031-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L031-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -18160,7 +18416,7 @@
       <c r="Y160" s="2" t="inlineStr"/>
       <c r="Z160" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -18197,12 +18453,12 @@
       <c r="J161" s="3" t="inlineStr"/>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W</t>
+          <t>1G-GGRQ-GQ-L032-F024-W</t>
         </is>
       </c>
       <c r="L161" s="3" t="inlineStr">
         <is>
-          <t>L032-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L032-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M161" s="3" t="inlineStr">
@@ -18268,7 +18524,7 @@
       <c r="Y161" s="3" t="inlineStr"/>
       <c r="Z161" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18636,7 @@
       </c>
       <c r="Z162" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -18492,7 +18748,7 @@
       </c>
       <c r="Z163" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -18604,7 +18860,7 @@
       </c>
       <c r="Z164" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -18716,7 +18972,7 @@
       </c>
       <c r="Z165" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -18828,7 +19084,7 @@
       </c>
       <c r="Z166" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -18940,7 +19196,7 @@
       </c>
       <c r="Z167" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19052,7 +19308,7 @@
       </c>
       <c r="Z168" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19420,7 @@
       </c>
       <c r="Z169" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19276,7 +19532,7 @@
       </c>
       <c r="Z170" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19388,7 +19644,7 @@
       </c>
       <c r="Z171" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19500,7 +19756,7 @@
       </c>
       <c r="Z172" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19612,7 +19868,7 @@
       </c>
       <c r="Z173" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19724,7 +19980,7 @@
       </c>
       <c r="Z174" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19836,7 +20092,7 @@
       </c>
       <c r="Z175" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -19948,7 +20204,7 @@
       </c>
       <c r="Z176" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20060,7 +20316,7 @@
       </c>
       <c r="Z177" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20172,7 +20428,7 @@
       </c>
       <c r="Z178" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20284,7 +20540,7 @@
       </c>
       <c r="Z179" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20396,7 +20652,7 @@
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20764,7 @@
       </c>
       <c r="Z181" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20620,7 +20876,7 @@
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20988,7 @@
       </c>
       <c r="Z183" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20844,7 +21100,7 @@
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -20956,7 +21212,7 @@
       </c>
       <c r="Z185" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21068,7 +21324,7 @@
       </c>
       <c r="Z186" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21436,7 @@
       </c>
       <c r="Z187" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21292,7 +21548,7 @@
       </c>
       <c r="Z188" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21404,7 +21660,7 @@
       </c>
       <c r="Z189" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21516,7 +21772,7 @@
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21628,7 +21884,7 @@
       </c>
       <c r="Z191" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21740,7 +21996,7 @@
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21852,7 +22108,7 @@
       </c>
       <c r="Z193" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -21964,7 +22220,7 @@
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22076,7 +22332,7 @@
       </c>
       <c r="Z195" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22188,7 +22444,7 @@
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22300,7 +22556,7 @@
       </c>
       <c r="Z197" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22412,7 +22668,7 @@
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22780,7 @@
       </c>
       <c r="Z199" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22892,7 @@
       </c>
       <c r="Z200" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22748,7 +23004,7 @@
       </c>
       <c r="Z201" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22860,7 +23116,7 @@
       </c>
       <c r="Z202" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -22972,7 +23228,7 @@
       </c>
       <c r="Z203" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23084,7 +23340,7 @@
       </c>
       <c r="Z204" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23196,7 +23452,7 @@
       </c>
       <c r="Z205" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23564,7 @@
       </c>
       <c r="Z206" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23420,7 +23676,7 @@
       </c>
       <c r="Z207" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23532,7 +23788,7 @@
       </c>
       <c r="Z208" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23644,7 +23900,7 @@
       </c>
       <c r="Z209" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23756,7 +24012,7 @@
       </c>
       <c r="Z210" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23868,7 +24124,7 @@
       </c>
       <c r="Z211" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -23980,7 +24236,7 @@
       </c>
       <c r="Z212" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24092,7 +24348,7 @@
       </c>
       <c r="Z213" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24460,7 @@
       </c>
       <c r="Z214" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24316,7 +24572,7 @@
       </c>
       <c r="Z215" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24428,7 +24684,7 @@
       </c>
       <c r="Z216" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24540,7 +24796,7 @@
       </c>
       <c r="Z217" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24652,7 +24908,7 @@
       </c>
       <c r="Z218" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24764,7 +25020,7 @@
       </c>
       <c r="Z219" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24876,7 +25132,7 @@
       </c>
       <c r="Z220" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -24988,7 +25244,7 @@
       </c>
       <c r="Z221" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25100,7 +25356,7 @@
       </c>
       <c r="Z222" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25212,7 +25468,7 @@
       </c>
       <c r="Z223" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25324,7 +25580,7 @@
       </c>
       <c r="Z224" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25436,7 +25692,7 @@
       </c>
       <c r="Z225" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25548,7 +25804,7 @@
       </c>
       <c r="Z226" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25660,7 +25916,7 @@
       </c>
       <c r="Z227" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25772,7 +26028,7 @@
       </c>
       <c r="Z228" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25884,7 +26140,7 @@
       </c>
       <c r="Z229" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -25996,7 +26252,7 @@
       </c>
       <c r="Z230" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -26108,7 +26364,7 @@
       </c>
       <c r="Z231" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -26220,7 +26476,7 @@
       </c>
       <c r="Z232" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -26332,7 +26588,7 @@
       </c>
       <c r="Z233" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26700,7 @@
       </c>
       <c r="Z234" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -26556,7 +26812,7 @@
       </c>
       <c r="Z235" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -26668,7 +26924,7 @@
       </c>
       <c r="Z236" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -26780,7 +27036,7 @@
       </c>
       <c r="Z237" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -26892,7 +27148,7 @@
       </c>
       <c r="Z238" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27004,7 +27260,7 @@
       </c>
       <c r="Z239" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27116,7 +27372,7 @@
       </c>
       <c r="Z240" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27484,7 @@
       </c>
       <c r="Z241" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27340,7 +27596,7 @@
       </c>
       <c r="Z242" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27452,7 +27708,7 @@
       </c>
       <c r="Z243" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27564,7 +27820,7 @@
       </c>
       <c r="Z244" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27676,7 +27932,7 @@
       </c>
       <c r="Z245" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27788,7 +28044,7 @@
       </c>
       <c r="Z246" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -27900,7 +28156,7 @@
       </c>
       <c r="Z247" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28012,7 +28268,7 @@
       </c>
       <c r="Z248" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28124,7 +28380,7 @@
       </c>
       <c r="Z249" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28236,7 +28492,7 @@
       </c>
       <c r="Z250" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28348,7 +28604,7 @@
       </c>
       <c r="Z251" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28460,7 +28716,7 @@
       </c>
       <c r="Z252" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28572,7 +28828,7 @@
       </c>
       <c r="Z253" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28684,7 +28940,7 @@
       </c>
       <c r="Z254" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28796,7 +29052,7 @@
       </c>
       <c r="Z255" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -28908,7 +29164,7 @@
       </c>
       <c r="Z256" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29020,7 +29276,7 @@
       </c>
       <c r="Z257" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29136,7 +29392,7 @@
       </c>
       <c r="Z258" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29252,7 +29508,7 @@
       </c>
       <c r="Z259" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29368,7 +29624,7 @@
       </c>
       <c r="Z260" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29484,7 +29740,7 @@
       </c>
       <c r="Z261" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29600,7 +29856,7 @@
       </c>
       <c r="Z262" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29716,7 +29972,7 @@
       </c>
       <c r="Z263" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29832,7 +30088,7 @@
       </c>
       <c r="Z264" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -29948,7 +30204,7 @@
       </c>
       <c r="Z265" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30064,7 +30320,7 @@
       </c>
       <c r="Z266" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30180,7 +30436,7 @@
       </c>
       <c r="Z267" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30296,7 +30552,7 @@
       </c>
       <c r="Z268" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30412,7 +30668,7 @@
       </c>
       <c r="Z269" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30528,7 +30784,7 @@
       </c>
       <c r="Z270" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30644,7 +30900,7 @@
       </c>
       <c r="Z271" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30760,7 +31016,7 @@
       </c>
       <c r="Z272" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30876,7 +31132,7 @@
       </c>
       <c r="Z273" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -30992,7 +31248,7 @@
       </c>
       <c r="Z274" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -31108,7 +31364,7 @@
       </c>
       <c r="Z275" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31480,7 @@
       </c>
       <c r="Z276" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -31340,7 +31596,7 @@
       </c>
       <c r="Z277" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -31456,7 +31712,7 @@
       </c>
       <c r="Z278" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -31572,7 +31828,7 @@
       </c>
       <c r="Z279" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -31688,7 +31944,7 @@
       </c>
       <c r="Z280" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -31804,7 +32060,7 @@
       </c>
       <c r="Z281" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -31920,7 +32176,7 @@
       </c>
       <c r="Z282" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32036,7 +32292,7 @@
       </c>
       <c r="Z283" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32152,7 +32408,7 @@
       </c>
       <c r="Z284" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32268,7 +32524,7 @@
       </c>
       <c r="Z285" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32384,7 +32640,7 @@
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32500,7 +32756,7 @@
       </c>
       <c r="Z287" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32616,7 +32872,7 @@
       </c>
       <c r="Z288" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32732,7 +32988,7 @@
       </c>
       <c r="Z289" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32848,7 +33104,7 @@
       </c>
       <c r="Z290" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -32964,7 +33220,7 @@
       </c>
       <c r="Z291" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -33080,7 +33336,7 @@
       </c>
       <c r="Z292" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -33196,7 +33452,7 @@
       </c>
       <c r="Z293" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -33312,7 +33568,7 @@
       </c>
       <c r="Z294" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -33428,7 +33684,7 @@
       </c>
       <c r="Z295" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -33544,7 +33800,7 @@
       </c>
       <c r="Z296" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -33660,7 +33916,7 @@
       </c>
       <c r="Z297" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -33776,7 +34032,7 @@
       </c>
       <c r="Z298" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -33892,7 +34148,7 @@
       </c>
       <c r="Z299" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34008,7 +34264,7 @@
       </c>
       <c r="Z300" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34124,7 +34380,7 @@
       </c>
       <c r="Z301" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34240,7 +34496,7 @@
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34356,7 +34612,7 @@
       </c>
       <c r="Z303" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34472,7 +34728,7 @@
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34588,7 +34844,7 @@
       </c>
       <c r="Z305" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34704,7 +34960,7 @@
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34820,7 +35076,7 @@
       </c>
       <c r="Z307" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -34936,7 +35192,7 @@
       </c>
       <c r="Z308" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35052,7 +35308,7 @@
       </c>
       <c r="Z309" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35168,7 +35424,7 @@
       </c>
       <c r="Z310" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35284,7 +35540,7 @@
       </c>
       <c r="Z311" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35400,7 +35656,7 @@
       </c>
       <c r="Z312" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35516,7 +35772,7 @@
       </c>
       <c r="Z313" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35628,7 +35884,7 @@
       </c>
       <c r="Z314" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35740,7 +35996,7 @@
       </c>
       <c r="Z315" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35852,7 +36108,7 @@
       </c>
       <c r="Z316" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -35964,7 +36220,7 @@
       </c>
       <c r="Z317" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36076,7 +36332,7 @@
       </c>
       <c r="Z318" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36188,7 +36444,7 @@
       </c>
       <c r="Z319" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36300,7 +36556,7 @@
       </c>
       <c r="Z320" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36412,7 +36668,7 @@
       </c>
       <c r="Z321" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36524,7 +36780,7 @@
       </c>
       <c r="Z322" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36636,7 +36892,7 @@
       </c>
       <c r="Z323" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36748,7 +37004,7 @@
       </c>
       <c r="Z324" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36860,7 +37116,7 @@
       </c>
       <c r="Z325" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -36972,7 +37228,7 @@
       </c>
       <c r="Z326" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37084,7 +37340,7 @@
       </c>
       <c r="Z327" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37196,7 +37452,7 @@
       </c>
       <c r="Z328" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37308,7 +37564,7 @@
       </c>
       <c r="Z329" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37420,7 +37676,7 @@
       </c>
       <c r="Z330" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37532,7 +37788,7 @@
       </c>
       <c r="Z331" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37644,7 +37900,7 @@
       </c>
       <c r="Z332" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37756,7 +38012,7 @@
       </c>
       <c r="Z333" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37868,7 +38124,7 @@
       </c>
       <c r="Z334" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -37980,7 +38236,7 @@
       </c>
       <c r="Z335" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38092,7 +38348,7 @@
       </c>
       <c r="Z336" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38204,7 +38460,7 @@
       </c>
       <c r="Z337" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38316,7 +38572,7 @@
       </c>
       <c r="Z338" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38428,7 +38684,7 @@
       </c>
       <c r="Z339" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38540,7 +38796,7 @@
       </c>
       <c r="Z340" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38652,7 +38908,7 @@
       </c>
       <c r="Z341" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38764,7 +39020,7 @@
       </c>
       <c r="Z342" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38876,7 +39132,7 @@
       </c>
       <c r="Z343" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -38988,7 +39244,7 @@
       </c>
       <c r="Z344" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39100,7 +39356,7 @@
       </c>
       <c r="Z345" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39212,7 +39468,7 @@
       </c>
       <c r="Z346" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39324,7 +39580,7 @@
       </c>
       <c r="Z347" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39436,7 +39692,7 @@
       </c>
       <c r="Z348" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39548,7 +39804,7 @@
       </c>
       <c r="Z349" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39660,7 +39916,7 @@
       </c>
       <c r="Z350" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39772,7 +40028,7 @@
       </c>
       <c r="Z351" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39884,7 +40140,7 @@
       </c>
       <c r="Z352" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -39996,7 +40252,7 @@
       </c>
       <c r="Z353" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -40108,7 +40364,7 @@
       </c>
       <c r="Z354" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -40220,7 +40476,7 @@
       </c>
       <c r="Z355" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -40332,7 +40588,7 @@
       </c>
       <c r="Z356" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -40444,7 +40700,7 @@
       </c>
       <c r="Z357" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -40556,7 +40812,7 @@
       </c>
       <c r="Z358" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -40668,7 +40924,7 @@
       </c>
       <c r="Z359" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -40780,7 +41036,7 @@
       </c>
       <c r="Z360" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -40892,7 +41148,7 @@
       </c>
       <c r="Z361" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41004,7 +41260,7 @@
       </c>
       <c r="Z362" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41116,7 +41372,7 @@
       </c>
       <c r="Z363" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41228,7 +41484,7 @@
       </c>
       <c r="Z364" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41340,7 +41596,7 @@
       </c>
       <c r="Z365" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41452,7 +41708,7 @@
       </c>
       <c r="Z366" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41564,7 +41820,7 @@
       </c>
       <c r="Z367" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41676,7 +41932,7 @@
       </c>
       <c r="Z368" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41788,7 +42044,7 @@
       </c>
       <c r="Z369" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -41900,7 +42156,7 @@
       </c>
       <c r="Z370" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42012,7 +42268,7 @@
       </c>
       <c r="Z371" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42124,7 +42380,7 @@
       </c>
       <c r="Z372" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42236,7 +42492,7 @@
       </c>
       <c r="Z373" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42348,7 +42604,7 @@
       </c>
       <c r="Z374" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42460,7 +42716,7 @@
       </c>
       <c r="Z375" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42572,7 +42828,7 @@
       </c>
       <c r="Z376" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42684,7 +42940,7 @@
       </c>
       <c r="Z377" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42796,7 +43052,7 @@
       </c>
       <c r="Z378" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -42908,7 +43164,7 @@
       </c>
       <c r="Z379" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43020,7 +43276,7 @@
       </c>
       <c r="Z380" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43132,7 +43388,7 @@
       </c>
       <c r="Z381" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43244,7 +43500,7 @@
       </c>
       <c r="Z382" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43356,7 +43612,7 @@
       </c>
       <c r="Z383" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43468,7 +43724,7 @@
       </c>
       <c r="Z384" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43580,7 +43836,7 @@
       </c>
       <c r="Z385" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43692,7 +43948,7 @@
       </c>
       <c r="Z386" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43804,7 +44060,7 @@
       </c>
       <c r="Z387" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -43916,7 +44172,7 @@
       </c>
       <c r="Z388" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44028,7 +44284,7 @@
       </c>
       <c r="Z389" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44140,7 +44396,7 @@
       </c>
       <c r="Z390" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44252,7 +44508,7 @@
       </c>
       <c r="Z391" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44364,7 +44620,7 @@
       </c>
       <c r="Z392" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44476,7 +44732,7 @@
       </c>
       <c r="Z393" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44588,7 +44844,7 @@
       </c>
       <c r="Z394" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44700,7 +44956,7 @@
       </c>
       <c r="Z395" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44812,7 +45068,7 @@
       </c>
       <c r="Z396" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -44924,7 +45180,7 @@
       </c>
       <c r="Z397" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45036,7 +45292,7 @@
       </c>
       <c r="Z398" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45148,7 +45404,7 @@
       </c>
       <c r="Z399" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45260,7 +45516,7 @@
       </c>
       <c r="Z400" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45372,7 +45628,7 @@
       </c>
       <c r="Z401" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45484,7 +45740,7 @@
       </c>
       <c r="Z402" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45596,7 +45852,7 @@
       </c>
       <c r="Z403" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45708,7 +45964,7 @@
       </c>
       <c r="Z404" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45820,7 +46076,7 @@
       </c>
       <c r="Z405" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -45932,7 +46188,7 @@
       </c>
       <c r="Z406" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46044,7 +46300,7 @@
       </c>
       <c r="Z407" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46156,7 +46412,7 @@
       </c>
       <c r="Z408" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46268,7 +46524,7 @@
       </c>
       <c r="Z409" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46384,7 +46640,7 @@
       </c>
       <c r="Z410" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46500,7 +46756,7 @@
       </c>
       <c r="Z411" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46872,7 @@
       </c>
       <c r="Z412" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46732,7 +46988,7 @@
       </c>
       <c r="Z413" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46848,7 +47104,7 @@
       </c>
       <c r="Z414" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -46964,7 +47220,7 @@
       </c>
       <c r="Z415" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -47080,7 +47336,7 @@
       </c>
       <c r="Z416" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -47196,7 +47452,7 @@
       </c>
       <c r="Z417" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -47312,7 +47568,7 @@
       </c>
       <c r="Z418" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -47428,7 +47684,7 @@
       </c>
       <c r="Z419" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -47544,7 +47800,7 @@
       </c>
       <c r="Z420" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -47660,7 +47916,7 @@
       </c>
       <c r="Z421" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -47776,7 +48032,7 @@
       </c>
       <c r="Z422" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -47892,7 +48148,7 @@
       </c>
       <c r="Z423" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48008,7 +48264,7 @@
       </c>
       <c r="Z424" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48124,7 +48380,7 @@
       </c>
       <c r="Z425" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48240,7 +48496,7 @@
       </c>
       <c r="Z426" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48612,7 @@
       </c>
       <c r="Z427" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48472,7 +48728,7 @@
       </c>
       <c r="Z428" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48588,7 +48844,7 @@
       </c>
       <c r="Z429" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48704,7 +48960,7 @@
       </c>
       <c r="Z430" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48820,7 +49076,7 @@
       </c>
       <c r="Z431" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -48936,7 +49192,7 @@
       </c>
       <c r="Z432" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49052,7 +49308,7 @@
       </c>
       <c r="Z433" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49168,7 +49424,7 @@
       </c>
       <c r="Z434" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49284,7 +49540,7 @@
       </c>
       <c r="Z435" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49400,7 +49656,7 @@
       </c>
       <c r="Z436" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49516,7 +49772,7 @@
       </c>
       <c r="Z437" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49632,7 +49888,7 @@
       </c>
       <c r="Z438" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49748,7 +50004,7 @@
       </c>
       <c r="Z439" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49864,7 +50120,7 @@
       </c>
       <c r="Z440" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -49980,7 +50236,7 @@
       </c>
       <c r="Z441" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50352,7 @@
       </c>
       <c r="Z442" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -50212,7 +50468,7 @@
       </c>
       <c r="Z443" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -50328,7 +50584,7 @@
       </c>
       <c r="Z444" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -50444,7 +50700,7 @@
       </c>
       <c r="Z445" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -50560,7 +50816,7 @@
       </c>
       <c r="Z446" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -50676,7 +50932,7 @@
       </c>
       <c r="Z447" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -50792,7 +51048,7 @@
       </c>
       <c r="Z448" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -50908,7 +51164,7 @@
       </c>
       <c r="Z449" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51024,7 +51280,7 @@
       </c>
       <c r="Z450" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51140,7 +51396,7 @@
       </c>
       <c r="Z451" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51256,7 +51512,7 @@
       </c>
       <c r="Z452" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51372,7 +51628,7 @@
       </c>
       <c r="Z453" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51488,7 +51744,7 @@
       </c>
       <c r="Z454" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51604,7 +51860,7 @@
       </c>
       <c r="Z455" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51720,7 +51976,7 @@
       </c>
       <c r="Z456" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51836,7 +52092,7 @@
       </c>
       <c r="Z457" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -51952,7 +52208,7 @@
       </c>
       <c r="Z458" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -52068,7 +52324,7 @@
       </c>
       <c r="Z459" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -52184,7 +52440,7 @@
       </c>
       <c r="Z460" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -52300,7 +52556,7 @@
       </c>
       <c r="Z461" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -52416,7 +52672,7 @@
       </c>
       <c r="Z462" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -52532,7 +52788,7 @@
       </c>
       <c r="Z463" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -52648,7 +52904,7 @@
       </c>
       <c r="Z464" s="2" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -52764,7 +53020,7 @@
       </c>
       <c r="Z465" s="3" t="inlineStr">
         <is>
-          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
     </row>
@@ -53334,7 +53590,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -53442,7 +53698,7 @@
       <c r="Y3" s="3" t="inlineStr"/>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -53550,7 +53806,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -53658,7 +53914,7 @@
       <c r="Y5" s="3" t="inlineStr"/>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -53766,7 +54022,7 @@
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -53874,7 +54130,7 @@
       <c r="Y7" s="3" t="inlineStr"/>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -53982,7 +54238,7 @@
       <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54090,7 +54346,7 @@
       <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54198,7 +54454,7 @@
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54306,7 +54562,7 @@
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54414,7 +54670,7 @@
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54522,7 +54778,7 @@
       <c r="Y13" s="3" t="inlineStr"/>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54630,7 +54886,7 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54738,7 +54994,7 @@
       <c r="Y15" s="3" t="inlineStr"/>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54846,7 +55102,7 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -54954,7 +55210,7 @@
       <c r="Y17" s="3" t="inlineStr"/>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55062,7 +55318,7 @@
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55170,7 +55426,7 @@
       <c r="Y19" s="3" t="inlineStr"/>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55278,7 +55534,7 @@
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55386,7 +55642,7 @@
       <c r="Y21" s="3" t="inlineStr"/>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55494,7 +55750,7 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55602,7 +55858,7 @@
       <c r="Y23" s="3" t="inlineStr"/>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55710,7 +55966,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55818,7 +56074,7 @@
       <c r="Y25" s="3" t="inlineStr"/>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -55926,7 +56182,7 @@
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56034,7 +56290,7 @@
       <c r="Y27" s="3" t="inlineStr"/>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56142,7 +56398,7 @@
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56250,7 +56506,7 @@
       <c r="Y29" s="3" t="inlineStr"/>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56358,7 +56614,7 @@
       <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56722,7 @@
       <c r="Y31" s="3" t="inlineStr"/>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56574,7 +56830,7 @@
       <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56682,7 +56938,7 @@
       <c r="Y33" s="3" t="inlineStr"/>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56790,7 +57046,7 @@
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -56898,7 +57154,7 @@
       <c r="Y35" s="3" t="inlineStr"/>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57006,7 +57262,7 @@
       <c r="Y36" s="2" t="inlineStr"/>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57114,7 +57370,7 @@
       <c r="Y37" s="3" t="inlineStr"/>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57222,7 +57478,7 @@
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57330,7 +57586,7 @@
       <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57438,7 +57694,7 @@
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57546,7 +57802,7 @@
       <c r="Y41" s="3" t="inlineStr"/>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57654,7 +57910,7 @@
       <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57762,7 +58018,7 @@
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57870,7 +58126,7 @@
       <c r="Y44" s="2" t="inlineStr"/>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -57978,7 +58234,7 @@
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58086,7 +58342,7 @@
       <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58194,7 +58450,7 @@
       <c r="Y47" s="3" t="inlineStr"/>
       <c r="Z47" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58302,7 +58558,7 @@
       <c r="Y48" s="2" t="inlineStr"/>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58410,7 +58666,7 @@
       <c r="Y49" s="3" t="inlineStr"/>
       <c r="Z49" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58774,7 @@
       <c r="Y50" s="2" t="inlineStr"/>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58626,7 +58882,7 @@
       <c r="Y51" s="3" t="inlineStr"/>
       <c r="Z51" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58734,7 +58990,7 @@
       <c r="Y52" s="2" t="inlineStr"/>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58842,7 +59098,7 @@
       <c r="Y53" s="3" t="inlineStr"/>
       <c r="Z53" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -58950,7 +59206,7 @@
       <c r="Y54" s="2" t="inlineStr"/>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -59058,7 +59314,7 @@
       <c r="Y55" s="3" t="inlineStr"/>
       <c r="Z55" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -59166,7 +59422,7 @@
       <c r="Y56" s="2" t="inlineStr"/>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -59274,7 +59530,7 @@
       <c r="Y57" s="3" t="inlineStr"/>
       <c r="Z57" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -59382,7 +59638,7 @@
       <c r="Y58" s="2" t="inlineStr"/>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -59490,7 +59746,7 @@
       <c r="Y59" s="3" t="inlineStr"/>
       <c r="Z59" s="3" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -59598,7 +59854,7 @@
       <c r="Y60" s="2" t="inlineStr"/>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
     </row>
@@ -59635,12 +59891,12 @@
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W</t>
+          <t>1G-GGRQ-GQ-L001-F024-W</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>L001-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L001-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -59706,7 +59962,7 @@
       <c r="Y61" s="3" t="inlineStr"/>
       <c r="Z61" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -59743,12 +59999,12 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W</t>
+          <t>1G-GGRQ-GQ-L002-F024-W</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>L002-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L002-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -59814,7 +60070,7 @@
       <c r="Y62" s="2" t="inlineStr"/>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -59851,12 +60107,12 @@
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W</t>
+          <t>1G-GGRQ-GQ-L003-F024-W</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>L003-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L003-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -59922,7 +60178,7 @@
       <c r="Y63" s="3" t="inlineStr"/>
       <c r="Z63" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -59959,12 +60215,12 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W</t>
+          <t>1G-GGRQ-GQ-L004-F024-W</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>L004-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L004-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -60030,7 +60286,7 @@
       <c r="Y64" s="2" t="inlineStr"/>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60067,12 +60323,12 @@
       <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W</t>
+          <t>1G-GGRQ-GQ-L005-F024-W</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>L005-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L005-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -60138,7 +60394,7 @@
       <c r="Y65" s="3" t="inlineStr"/>
       <c r="Z65" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60175,12 +60431,12 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W</t>
+          <t>1G-GGRQ-GQ-L006-F024-W</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>L006-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L006-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -60246,7 +60502,7 @@
       <c r="Y66" s="2" t="inlineStr"/>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60283,12 +60539,12 @@
       <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W</t>
+          <t>1G-GGRQ-GQ-L007-F024-W</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>L007-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L007-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -60354,7 +60610,7 @@
       <c r="Y67" s="3" t="inlineStr"/>
       <c r="Z67" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60391,12 +60647,12 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W</t>
+          <t>1G-GGRQ-GQ-L008-F024-W</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>L008-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L008-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -60462,7 +60718,7 @@
       <c r="Y68" s="2" t="inlineStr"/>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60499,12 +60755,12 @@
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W</t>
+          <t>1G-GGRQ-GQ-L009-F024-W</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>L009-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L009-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -60570,7 +60826,7 @@
       <c r="Y69" s="3" t="inlineStr"/>
       <c r="Z69" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60607,12 +60863,12 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W</t>
+          <t>1G-GGRQ-GQ-L010-F024-W</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>L010-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L010-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -60678,7 +60934,7 @@
       <c r="Y70" s="2" t="inlineStr"/>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60715,12 +60971,12 @@
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W</t>
+          <t>1G-GGRQ-GQ-L011-F024-W</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>L011-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L011-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
@@ -60786,7 +61042,7 @@
       <c r="Y71" s="3" t="inlineStr"/>
       <c r="Z71" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60823,12 +61079,12 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W</t>
+          <t>1G-GGRQ-GQ-L012-F024-W</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>L012-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L012-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -60894,7 +61150,7 @@
       <c r="Y72" s="2" t="inlineStr"/>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -60931,12 +61187,12 @@
       <c r="J73" s="3" t="inlineStr"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W</t>
+          <t>1G-GGRQ-GQ-L013-F024-W</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>L013-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L013-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
@@ -61002,7 +61258,7 @@
       <c r="Y73" s="3" t="inlineStr"/>
       <c r="Z73" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61039,12 +61295,12 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W</t>
+          <t>1G-GGRQ-GQ-L014-F024-W</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>L014-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L014-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -61110,7 +61366,7 @@
       <c r="Y74" s="2" t="inlineStr"/>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61147,12 +61403,12 @@
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W</t>
+          <t>1G-GGRQ-GQ-L015-F024-W</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>L015-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L015-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -61218,7 +61474,7 @@
       <c r="Y75" s="3" t="inlineStr"/>
       <c r="Z75" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61255,12 +61511,12 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W</t>
+          <t>1G-GGRQ-GQ-L016-F024-W</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>L016-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L016-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -61326,7 +61582,7 @@
       <c r="Y76" s="2" t="inlineStr"/>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61363,12 +61619,12 @@
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W</t>
+          <t>1G-GGRQ-GQ-L017-F024-W</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>L017-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L017-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -61434,7 +61690,7 @@
       <c r="Y77" s="3" t="inlineStr"/>
       <c r="Z77" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61471,12 +61727,12 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W</t>
+          <t>1G-GGRQ-GQ-L018-F024-W</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>L018-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L018-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -61542,7 +61798,7 @@
       <c r="Y78" s="2" t="inlineStr"/>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61579,12 +61835,12 @@
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W</t>
+          <t>1G-GGRQ-GQ-L019-F024-W</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>L019-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L019-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -61650,7 +61906,7 @@
       <c r="Y79" s="3" t="inlineStr"/>
       <c r="Z79" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61687,12 +61943,12 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W</t>
+          <t>1G-GGRQ-GQ-L020-F024-W</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>L020-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L020-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -61758,7 +62014,7 @@
       <c r="Y80" s="2" t="inlineStr"/>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61795,12 +62051,12 @@
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W</t>
+          <t>1G-GGRQ-GQ-L021-F024-W</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>L021-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L021-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -61866,7 +62122,7 @@
       <c r="Y81" s="3" t="inlineStr"/>
       <c r="Z81" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -61903,12 +62159,12 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W</t>
+          <t>1G-GGRQ-GQ-L022-F024-W</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>L022-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L022-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -61974,7 +62230,7 @@
       <c r="Y82" s="2" t="inlineStr"/>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62011,12 +62267,12 @@
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W</t>
+          <t>1G-GGRQ-GQ-L023-F024-W</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>L023-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L023-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -62082,7 +62338,7 @@
       <c r="Y83" s="3" t="inlineStr"/>
       <c r="Z83" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62119,12 +62375,12 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W</t>
+          <t>1G-GGRQ-GQ-L024-F024-W</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>L024-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L024-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -62190,7 +62446,7 @@
       <c r="Y84" s="2" t="inlineStr"/>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62227,12 +62483,12 @@
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W</t>
+          <t>1G-GGRQ-GQ-L025-F024-W</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>L025-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L025-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -62298,7 +62554,7 @@
       <c r="Y85" s="3" t="inlineStr"/>
       <c r="Z85" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62335,12 +62591,12 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W</t>
+          <t>1G-GGRQ-GQ-L026-F024-W</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>L026-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L026-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -62406,7 +62662,7 @@
       <c r="Y86" s="2" t="inlineStr"/>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62443,12 +62699,12 @@
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W</t>
+          <t>1G-GGRQ-GQ-L027-F024-W</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>L027-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L027-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
@@ -62514,7 +62770,7 @@
       <c r="Y87" s="3" t="inlineStr"/>
       <c r="Z87" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62551,12 +62807,12 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W</t>
+          <t>1G-GGRQ-GQ-L028-F024-W</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>L028-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L028-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -62622,7 +62878,7 @@
       <c r="Y88" s="2" t="inlineStr"/>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62659,12 +62915,12 @@
       <c r="J89" s="3" t="inlineStr"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W</t>
+          <t>1G-GGRQ-GQ-L029-F024-W</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>L029-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L029-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
@@ -62730,7 +62986,7 @@
       <c r="Y89" s="3" t="inlineStr"/>
       <c r="Z89" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62767,12 +63023,12 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W</t>
+          <t>1G-GGRQ-GQ-L030-F024-W</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>L030-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L030-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -62838,7 +63094,7 @@
       <c r="Y90" s="2" t="inlineStr"/>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62875,12 +63131,12 @@
       <c r="J91" s="3" t="inlineStr"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W</t>
+          <t>1G-GGRQ-GQ-L031-F024-W</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>L031-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L031-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
@@ -62946,7 +63202,7 @@
       <c r="Y91" s="3" t="inlineStr"/>
       <c r="Z91" s="3" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -62983,12 +63239,12 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W</t>
+          <t>1G-GGRQ-GQ-L032-F024-W</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>L032-B001；源位置：1-32屏的炉后第1根共32个弯头</t>
+          <t>L032-F024；源位置：1-32屏的炉后第1根共32个弯头</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -63054,7 +63310,7 @@
       <c r="Y92" s="2" t="inlineStr"/>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
     </row>
@@ -65889,7 +66145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -65941,12 +66197,12 @@
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UNCONFIRMED_ATTRIBUTES</t>
+          <t>SUMMARY_EXPANSION</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -65956,29 +66212,25 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>汇总行展开64条，含5条异常观察</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
-        </is>
-      </c>
+          <t>按本源行屏号/管位枚举；仅排除本批次本汇总的异常位置，不扣除其他年度检查</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="50" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED_ATTRIBUTES</t>
+          <t>SOURCE_SPEC_REVIEW</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -65993,22 +66245,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>本行明确规格Φ54×7.5、材质304H；材质304H与区带映射一致，Φ54×7.5与第4/5行配对(304H↔Φ51×8)不一致</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>全64项一律保留本源行单值，不把59项擅改Φ51×8</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>该汇总行真实规格及牌号</t>
         </is>
       </c>
     </row>
@@ -66030,12 +66282,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>汇总行展开64条，含5条异常观察</t>
+          <t>汇总行展开32条，含0条异常观察</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -66048,12 +66300,12 @@
     <row r="5" ht="50" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SOURCE_SPEC_REVIEW</t>
+          <t>GEOMETRY_CONFIRMED</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -66063,34 +66315,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>本行明确规格Φ54×7.5、材质304H；与其他行候选对应关系有疑点</t>
+          <t>高过每屏24根已由用户确认（F001–F024↔B024–B001、L001–L032↔R032–R001）</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>全64项一律保留本源行单值，不把59项擅改Φ51×8</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>该汇总行真实规格及牌号</t>
-        </is>
-      </c>
+          <t>炉后第N根镜像为F(25-N)规范方向；系统已启用同口径归一</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SUMMARY_EXPANSION</t>
+          <t>YEAR_PRECISION</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>高</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -66098,27 +66346,27 @@
           <t>2026年1号机C修</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>汇总行展开32条，含0条异常观察</t>
+          <t>只提供年份，未提供实际检测月日</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>按本源行屏号/管位枚举；仅排除本批次本汇总的异常位置，不扣除其他年度检查</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>日期写年份文本；每条描述注明日期精度=年；未生成01-01</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>实际检测日期（若可取得）</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED_GEOMETRY</t>
+          <t>UNCONFIRMED_ATTRIBUTES</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -66128,34 +66376,34 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026年1号机C修</t>
+          <t>2022年1号机A修</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>炉后B001与炉前F编号的换算需要实际总数，源表不能确认独立物理管总数</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>保留B001，不使用22/24假定总管数换算</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>每屏管/弯头/管圈的物理关系及总数</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>YEAR_PRECISION</t>
+          <t>UNCONFIRMED_ATTRIBUTES</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -66165,23 +66413,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>2022年1号机A修</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>只提供年份，未提供实际检测月日</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>日期写年份文本；每条描述注明日期精度=年；未生成01-01</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>实际检测日期（若可取得）</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66203,22 +66455,22 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66240,22 +66492,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66277,22 +66529,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66314,22 +66566,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66351,22 +66603,22 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66388,22 +66640,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66425,22 +66677,22 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66462,22 +66714,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66499,22 +66751,22 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66536,22 +66788,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66573,22 +66825,22 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66610,22 +66862,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66647,22 +66899,22 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66684,29 +66936,29 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
     <row r="23" ht="50" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED_ATTRIBUTES</t>
+          <t>YEAR_PRECISION</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -66719,24 +66971,20 @@
           <t>2022年1号机A修</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>只提供年份，未提供实际检测月日</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>日期写年份文本；每条描述注明日期精度=年；未生成01-01</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>实际检测日期（若可取得）</t>
         </is>
       </c>
     </row>
@@ -66753,34 +67001,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2022年1号机A修</t>
+          <t>2021年2号机A修</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
     <row r="25" ht="50" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>YEAR_PRECISION</t>
+          <t>UNCONFIRMED_ATTRIBUTES</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -66790,23 +67038,27 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2022年1号机A修</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr"/>
+          <t>2021年2号机A修</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>只提供年份，未提供实际检测月日</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>日期写年份文本；每条描述注明日期精度=年；未生成01-01</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>实际检测日期（若可取得）</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66828,22 +67080,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66865,22 +67117,22 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66902,22 +67154,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66939,22 +67191,22 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -66976,22 +67228,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67013,22 +67265,22 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67050,22 +67302,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67087,22 +67339,22 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67124,22 +67376,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67161,22 +67413,22 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67198,22 +67450,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67235,22 +67487,22 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67272,22 +67524,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
@@ -67309,29 +67561,29 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>多值材质/规格的逐管对应（12/7弯头区带与每屏24根的关系及计数方向）未确认</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>材质规格留空；候选列表和原备注保留在描述及审计</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>2022/2021的12/7弯头区带对应前12根还是后12根、按哪个方向计数</t>
         </is>
       </c>
     </row>
     <row r="40" ht="50" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>UNCONFIRMED_ATTRIBUTES</t>
+          <t>YEAR_PRECISION</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -67344,136 +67596,62 @@
           <t>2021年2号机A修</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>只提供年份，未提供实际检测月日</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>日期写年份文本；每条描述注明日期精度=年；未生成01-01</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
+          <t>实际检测日期（若可取得）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="50" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED_ATTRIBUTES</t>
+          <t>EXACT_DUPLICATE_QUARANTINED</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>阻断候选</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>2021年2号机A修</t>
+          <t>2026年1号机C修</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29/32</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>多值/缺失材质规格不能由W流水号分配；备注物理计数与编码方向需核证</t>
+          <t>与2026年1号机C修!R29#001的原编码、位置、方法、结果、规格材质和备注完全相同</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>仅源行单值进入规格/材质列；候选列表和原备注保留在描述及审计</t>
+          <t>第一条保留，重复候选保留审计但不导入；未补造第27屏合格记录</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>逐位置材质/规格 / 备注弯头组与F/B位置的对应关系</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="50" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>YEAR_PRECISION</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>2021年2号机A修</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>只提供年份，未提供实际检测月日</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>日期写年份文本；每条描述注明日期精度=年；未生成01-01</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>实际检测日期（若可取得）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="50" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>EXACT_DUPLICATE_QUARANTINED</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>阻断候选</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>2026年1号机C修</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>29/32</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>与2026年1号机C修!R29#001的原编码、位置、方法、结果、规格材质和备注完全相同</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>第一条保留，重复候选保留审计但不导入；未补造第27屏合格记录</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
           <t>重复第24屏是否应为第27屏或确为重复记录</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G43"/>
+  <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="0"/>
 </worksheet>

--- a/data-cleaning/verified/数据清洗审计.xlsx
+++ b/data-cleaning/verified/数据清洗审计.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>film-records-physical-codes-v8</t>
+          <t>film-records-physical-codes-v9</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U2" s="1" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="T3" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U3" s="1" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="T4" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U4" s="1" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="T5" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U5" s="1" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="T6" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U6" s="1" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="T7" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U7" s="1" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="T8" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U8" s="1" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="T9" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U9" s="1" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U10" s="1" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="T11" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U11" s="1" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="T12" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U12" s="1" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="T13" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U13" s="1" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="T14" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="T15" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U15" s="1" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="T16" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U16" s="1" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="T17" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U17" s="1" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="T18" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U18" s="1" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="T19" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="T20" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U20" s="1" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T21" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U21" s="1" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="T22" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U22" s="1" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="T23" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U23" s="1" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="T24" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U24" s="1" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="T25" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U25" s="1" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="T26" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U26" s="1" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="T27" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U27" s="1" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="T28" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U28" s="1" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="T29" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U29" s="1" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="T30" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U30" s="1" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="T31" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U31" s="1" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="T32" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U32" s="1" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="T33" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U33" s="1" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="T34" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U34" s="1" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="T35" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U35" s="1" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="T36" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U36" s="1" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="T37" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U37" s="1" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="T38" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U38" s="1" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="T39" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U39" s="1" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="T40" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U40" s="1" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="T41" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U41" s="1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="T42" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U42" s="1" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="T43" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U43" s="1" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="T44" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U44" s="1" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="T45" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U45" s="1" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="T46" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U46" s="1" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="T47" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U47" s="1" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="T48" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U48" s="1" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="T49" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U49" s="1" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="T50" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U50" s="1" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="T51" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U51" s="1" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="T52" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U52" s="1" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="T53" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U53" s="1" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="T54" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U54" s="1" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="T55" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U55" s="1" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="T56" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U56" s="1" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="T57" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U57" s="1" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="T58" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U58" s="1" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="T59" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U59" s="1" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="T60" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U60" s="1" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="T61" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U61" s="1" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="T62" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U62" s="1" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="T63" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U63" s="1" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="T64" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U64" s="1" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="T65" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U65" s="1" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="T66" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U66" s="1" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="T67" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U67" s="1" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="T68" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U68" s="1" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="T69" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U69" s="1" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="T70" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U70" s="1" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="T71" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U71" s="1" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="T72" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U72" s="1" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="T73" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U73" s="1" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="T74" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U74" s="1" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="T75" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U75" s="1" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="T76" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U76" s="1" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="T77" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U77" s="1" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="T78" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U78" s="1" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="T79" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U79" s="1" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="T80" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U80" s="1" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="T81" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U81" s="1" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="T82" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U82" s="1" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="T83" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U83" s="1" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="T84" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U84" s="1" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="T85" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U85" s="1" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="T86" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U86" s="1" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="T87" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U87" s="1" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="T88" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U88" s="1" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="T89" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U89" s="1" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="T90" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U90" s="1" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="T91" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U91" s="1" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="T92" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U92" s="1" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="T93" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U93" s="1" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="T94" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U94" s="1" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="T95" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U95" s="1" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="T96" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U96" s="1" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="T97" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U97" s="1" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="T98" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U98" s="1" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="T99" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U99" s="1" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="T100" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U100" s="1" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="T101" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U101" s="1" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="T102" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U102" s="1" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="T103" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U103" s="1" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="T104" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U104" s="1" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="T105" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U105" s="1" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="T106" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U106" s="1" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="T107" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U107" s="1" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="T108" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U108" s="1" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="T109" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U109" s="1" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="T110" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U110" s="1" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="T111" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U111" s="1" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="T112" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U112" s="1" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="T113" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U113" s="1" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="T114" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U114" s="1" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="T115" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U115" s="1" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="T116" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U116" s="1" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="T117" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U117" s="1" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="T118" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U118" s="1" t="inlineStr">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="T119" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U119" s="1" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="T120" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U120" s="1" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="T121" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U121" s="1" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="T122" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U122" s="1" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="T123" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U123" s="1" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="T124" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U124" s="1" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="T125" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U125" s="1" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="T126" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U126" s="1" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="T127" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U127" s="1" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="T128" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U128" s="1" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="T129" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U129" s="1" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="T130" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U130" s="1" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="T131" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U131" s="1" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="T132" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U132" s="1" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="T133" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U133" s="1" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="T134" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U134" s="1" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="T135" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U135" s="1" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="T136" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U136" s="1" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="T137" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U137" s="1" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="T138" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U138" s="1" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="T139" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U139" s="1" t="inlineStr">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="T140" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U140" s="1" t="inlineStr">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="T141" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U141" s="1" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="T142" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U142" s="1" t="inlineStr">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="T143" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U143" s="1" t="inlineStr">
@@ -16625,7 +16625,7 @@
       </c>
       <c r="T144" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U144" s="1" t="inlineStr">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="T145" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U145" s="1" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="T146" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U146" s="1" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="T147" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U147" s="1" t="inlineStr">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="T148" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U148" s="1" t="inlineStr">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="T149" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U149" s="1" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="T150" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U150" s="1" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="T151" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U151" s="1" t="inlineStr">
@@ -17489,7 +17489,7 @@
       </c>
       <c r="T152" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U152" s="1" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="T153" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U153" s="1" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="T154" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U154" s="1" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="T155" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U155" s="1" t="inlineStr">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="T156" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U156" s="1" t="inlineStr">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="T157" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U157" s="1" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="T158" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U158" s="1" t="inlineStr">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="T159" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U159" s="1" t="inlineStr">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="T160" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U160" s="1" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="T161" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U161" s="1" t="inlineStr">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="T162" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U162" s="1" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="T163" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U163" s="1" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="T164" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U164" s="1" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="T165" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U165" s="1" t="inlineStr">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="T166" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U166" s="1" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="T167" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U167" s="1" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="T168" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U168" s="1" t="inlineStr">
@@ -19417,7 +19417,7 @@
       </c>
       <c r="T169" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U169" s="1" t="inlineStr">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="T170" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U170" s="1" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="T171" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U171" s="1" t="inlineStr">
@@ -19777,7 +19777,7 @@
       </c>
       <c r="T172" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U172" s="1" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="T173" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U173" s="1" t="inlineStr">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="T174" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U174" s="1" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="T175" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U175" s="1" t="inlineStr">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="T176" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U176" s="1" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="T177" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U177" s="1" t="inlineStr">
@@ -20497,7 +20497,7 @@
       </c>
       <c r="T178" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U178" s="1" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="T179" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U179" s="1" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="T180" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U180" s="1" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="T181" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U181" s="1" t="inlineStr">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="T182" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U182" s="1" t="inlineStr">
@@ -21097,7 +21097,7 @@
       </c>
       <c r="T183" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U183" s="1" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="T184" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U184" s="1" t="inlineStr">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="T185" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U185" s="1" t="inlineStr">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="T186" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U186" s="1" t="inlineStr">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="T187" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U187" s="1" t="inlineStr">
@@ -21697,7 +21697,7 @@
       </c>
       <c r="T188" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U188" s="1" t="inlineStr">
@@ -21817,7 +21817,7 @@
       </c>
       <c r="T189" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U189" s="1" t="inlineStr">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="T190" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U190" s="1" t="inlineStr">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="T191" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U191" s="1" t="inlineStr">
@@ -22177,7 +22177,7 @@
       </c>
       <c r="T192" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U192" s="1" t="inlineStr">
@@ -22297,7 +22297,7 @@
       </c>
       <c r="T193" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U193" s="1" t="inlineStr">
@@ -22417,7 +22417,7 @@
       </c>
       <c r="T194" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U194" s="1" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="T195" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U195" s="1" t="inlineStr">
@@ -22657,7 +22657,7 @@
       </c>
       <c r="T196" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U196" s="1" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="T197" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U197" s="1" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="T198" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U198" s="1" t="inlineStr">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="T199" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U199" s="1" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="T200" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U200" s="1" t="inlineStr">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="T201" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U201" s="1" t="inlineStr">
@@ -23377,7 +23377,7 @@
       </c>
       <c r="T202" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U202" s="1" t="inlineStr">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="T203" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U203" s="1" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="T204" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U204" s="1" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="T205" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U205" s="1" t="inlineStr">
@@ -23857,7 +23857,7 @@
       </c>
       <c r="T206" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U206" s="1" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="T207" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U207" s="1" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="T208" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U208" s="1" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="T209" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U209" s="1" t="inlineStr">
@@ -24337,7 +24337,7 @@
       </c>
       <c r="T210" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U210" s="1" t="inlineStr">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="T211" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U211" s="1" t="inlineStr">
@@ -24577,7 +24577,7 @@
       </c>
       <c r="T212" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U212" s="1" t="inlineStr">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="T213" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U213" s="1" t="inlineStr">
@@ -24817,7 +24817,7 @@
       </c>
       <c r="T214" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U214" s="1" t="inlineStr">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="T215" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U215" s="1" t="inlineStr">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="T216" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U216" s="1" t="inlineStr">
@@ -25177,7 +25177,7 @@
       </c>
       <c r="T217" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U217" s="1" t="inlineStr">
@@ -25297,7 +25297,7 @@
       </c>
       <c r="T218" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U218" s="1" t="inlineStr">
@@ -25417,7 +25417,7 @@
       </c>
       <c r="T219" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U219" s="1" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="T220" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U220" s="1" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="T221" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U221" s="1" t="inlineStr">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="T222" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U222" s="1" t="inlineStr">
@@ -25897,7 +25897,7 @@
       </c>
       <c r="T223" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U223" s="1" t="inlineStr">
@@ -26017,7 +26017,7 @@
       </c>
       <c r="T224" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U224" s="1" t="inlineStr">
@@ -26137,7 +26137,7 @@
       </c>
       <c r="T225" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U225" s="1" t="inlineStr">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="T226" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U226" s="1" t="inlineStr">
@@ -26377,7 +26377,7 @@
       </c>
       <c r="T227" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U227" s="1" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="T228" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U228" s="1" t="inlineStr">
@@ -26617,7 +26617,7 @@
       </c>
       <c r="T229" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U229" s="1" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="T230" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U230" s="1" t="inlineStr">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="T231" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U231" s="1" t="inlineStr">
@@ -26977,7 +26977,7 @@
       </c>
       <c r="T232" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U232" s="1" t="inlineStr">
@@ -27097,7 +27097,7 @@
       </c>
       <c r="T233" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U233" s="1" t="inlineStr">
@@ -27217,7 +27217,7 @@
       </c>
       <c r="T234" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U234" s="1" t="inlineStr">
@@ -27337,7 +27337,7 @@
       </c>
       <c r="T235" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U235" s="1" t="inlineStr">
@@ -27457,7 +27457,7 @@
       </c>
       <c r="T236" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U236" s="1" t="inlineStr">
@@ -27577,7 +27577,7 @@
       </c>
       <c r="T237" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U237" s="1" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="T238" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U238" s="1" t="inlineStr">
@@ -27817,7 +27817,7 @@
       </c>
       <c r="T239" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U239" s="1" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="T240" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U240" s="1" t="inlineStr">
@@ -28057,7 +28057,7 @@
       </c>
       <c r="T241" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U241" s="1" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="T242" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U242" s="1" t="inlineStr">
@@ -28297,7 +28297,7 @@
       </c>
       <c r="T243" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U243" s="1" t="inlineStr">
@@ -28417,7 +28417,7 @@
       </c>
       <c r="T244" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U244" s="1" t="inlineStr">
@@ -28537,7 +28537,7 @@
       </c>
       <c r="T245" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U245" s="1" t="inlineStr">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="T246" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U246" s="1" t="inlineStr">
@@ -28777,7 +28777,7 @@
       </c>
       <c r="T247" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U247" s="1" t="inlineStr">
@@ -28897,7 +28897,7 @@
       </c>
       <c r="T248" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U248" s="1" t="inlineStr">
@@ -29017,7 +29017,7 @@
       </c>
       <c r="T249" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U249" s="1" t="inlineStr">
@@ -29137,7 +29137,7 @@
       </c>
       <c r="T250" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U250" s="1" t="inlineStr">
@@ -29257,7 +29257,7 @@
       </c>
       <c r="T251" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U251" s="1" t="inlineStr">
@@ -29377,7 +29377,7 @@
       </c>
       <c r="T252" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U252" s="1" t="inlineStr">
@@ -29497,7 +29497,7 @@
       </c>
       <c r="T253" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U253" s="1" t="inlineStr">
@@ -29617,7 +29617,7 @@
       </c>
       <c r="T254" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U254" s="1" t="inlineStr">
@@ -29737,7 +29737,7 @@
       </c>
       <c r="T255" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U255" s="1" t="inlineStr">
@@ -29857,7 +29857,7 @@
       </c>
       <c r="T256" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U256" s="1" t="inlineStr">
@@ -29977,7 +29977,7 @@
       </c>
       <c r="T257" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U257" s="1" t="inlineStr">
@@ -30097,7 +30097,7 @@
       </c>
       <c r="T258" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U258" s="1" t="inlineStr">
@@ -30217,7 +30217,7 @@
       </c>
       <c r="T259" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U259" s="1" t="inlineStr">
@@ -30337,7 +30337,7 @@
       </c>
       <c r="T260" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U260" s="1" t="inlineStr">
@@ -30457,7 +30457,7 @@
       </c>
       <c r="T261" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U261" s="1" t="inlineStr">
@@ -30577,7 +30577,7 @@
       </c>
       <c r="T262" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U262" s="1" t="inlineStr">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="T263" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U263" s="1" t="inlineStr">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="T264" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U264" s="1" t="inlineStr">
@@ -30937,7 +30937,7 @@
       </c>
       <c r="T265" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U265" s="1" t="inlineStr">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="T266" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U266" s="1" t="inlineStr">
@@ -31177,7 +31177,7 @@
       </c>
       <c r="T267" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U267" s="1" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="T268" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U268" s="1" t="inlineStr">
@@ -31417,7 +31417,7 @@
       </c>
       <c r="T269" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U269" s="1" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="T270" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U270" s="1" t="inlineStr">
@@ -31657,7 +31657,7 @@
       </c>
       <c r="T271" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U271" s="1" t="inlineStr">
@@ -31777,7 +31777,7 @@
       </c>
       <c r="T272" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U272" s="1" t="inlineStr">
@@ -31897,7 +31897,7 @@
       </c>
       <c r="T273" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U273" s="1" t="inlineStr">
@@ -32017,7 +32017,7 @@
       </c>
       <c r="T274" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U274" s="1" t="inlineStr">
@@ -32137,7 +32137,7 @@
       </c>
       <c r="T275" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U275" s="1" t="inlineStr">
@@ -32257,7 +32257,7 @@
       </c>
       <c r="T276" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U276" s="1" t="inlineStr">
@@ -32377,7 +32377,7 @@
       </c>
       <c r="T277" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U277" s="1" t="inlineStr">
@@ -32497,7 +32497,7 @@
       </c>
       <c r="T278" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U278" s="1" t="inlineStr">
@@ -32617,7 +32617,7 @@
       </c>
       <c r="T279" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U279" s="1" t="inlineStr">
@@ -32737,7 +32737,7 @@
       </c>
       <c r="T280" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U280" s="1" t="inlineStr">
@@ -32857,7 +32857,7 @@
       </c>
       <c r="T281" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U281" s="1" t="inlineStr">
@@ -32977,7 +32977,7 @@
       </c>
       <c r="T282" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U282" s="1" t="inlineStr">
@@ -33097,7 +33097,7 @@
       </c>
       <c r="T283" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U283" s="1" t="inlineStr">
@@ -33217,7 +33217,7 @@
       </c>
       <c r="T284" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U284" s="1" t="inlineStr">
@@ -33337,7 +33337,7 @@
       </c>
       <c r="T285" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U285" s="1" t="inlineStr">
@@ -33457,7 +33457,7 @@
       </c>
       <c r="T286" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U286" s="1" t="inlineStr">
@@ -33577,7 +33577,7 @@
       </c>
       <c r="T287" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U287" s="1" t="inlineStr">
@@ -33697,7 +33697,7 @@
       </c>
       <c r="T288" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U288" s="1" t="inlineStr">
@@ -33817,7 +33817,7 @@
       </c>
       <c r="T289" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U289" s="1" t="inlineStr">
@@ -33937,7 +33937,7 @@
       </c>
       <c r="T290" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U290" s="1" t="inlineStr">
@@ -34057,7 +34057,7 @@
       </c>
       <c r="T291" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U291" s="1" t="inlineStr">
@@ -34177,7 +34177,7 @@
       </c>
       <c r="T292" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U292" s="1" t="inlineStr">
@@ -34297,7 +34297,7 @@
       </c>
       <c r="T293" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U293" s="1" t="inlineStr">
@@ -34417,7 +34417,7 @@
       </c>
       <c r="T294" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U294" s="1" t="inlineStr">
@@ -34537,7 +34537,7 @@
       </c>
       <c r="T295" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U295" s="1" t="inlineStr">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="T296" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U296" s="1" t="inlineStr">
@@ -34777,7 +34777,7 @@
       </c>
       <c r="T297" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U297" s="1" t="inlineStr">
@@ -34897,7 +34897,7 @@
       </c>
       <c r="T298" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U298" s="1" t="inlineStr">
@@ -35017,7 +35017,7 @@
       </c>
       <c r="T299" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U299" s="1" t="inlineStr">
@@ -35137,7 +35137,7 @@
       </c>
       <c r="T300" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U300" s="1" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="T301" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U301" s="1" t="inlineStr">
@@ -35377,7 +35377,7 @@
       </c>
       <c r="T302" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U302" s="1" t="inlineStr">
@@ -35497,7 +35497,7 @@
       </c>
       <c r="T303" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U303" s="1" t="inlineStr">
@@ -35617,7 +35617,7 @@
       </c>
       <c r="T304" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U304" s="1" t="inlineStr">
@@ -35737,7 +35737,7 @@
       </c>
       <c r="T305" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U305" s="1" t="inlineStr">
@@ -35857,7 +35857,7 @@
       </c>
       <c r="T306" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U306" s="1" t="inlineStr">
@@ -35977,7 +35977,7 @@
       </c>
       <c r="T307" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U307" s="1" t="inlineStr">
@@ -36097,7 +36097,7 @@
       </c>
       <c r="T308" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U308" s="1" t="inlineStr">
@@ -36217,7 +36217,7 @@
       </c>
       <c r="T309" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U309" s="1" t="inlineStr">
@@ -36337,7 +36337,7 @@
       </c>
       <c r="T310" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U310" s="1" t="inlineStr">
@@ -36457,7 +36457,7 @@
       </c>
       <c r="T311" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U311" s="1" t="inlineStr">
@@ -36577,7 +36577,7 @@
       </c>
       <c r="T312" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U312" s="1" t="inlineStr">
@@ -36697,7 +36697,7 @@
       </c>
       <c r="T313" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U313" s="1" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="T314" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U314" s="1" t="inlineStr">
@@ -36937,7 +36937,7 @@
       </c>
       <c r="T315" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U315" s="1" t="inlineStr">
@@ -37057,7 +37057,7 @@
       </c>
       <c r="T316" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U316" s="1" t="inlineStr">
@@ -37177,7 +37177,7 @@
       </c>
       <c r="T317" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U317" s="1" t="inlineStr">
@@ -37297,7 +37297,7 @@
       </c>
       <c r="T318" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U318" s="1" t="inlineStr">
@@ -37417,7 +37417,7 @@
       </c>
       <c r="T319" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U319" s="1" t="inlineStr">
@@ -37537,7 +37537,7 @@
       </c>
       <c r="T320" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U320" s="1" t="inlineStr">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="T321" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U321" s="1" t="inlineStr">
@@ -37777,7 +37777,7 @@
       </c>
       <c r="T322" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U322" s="1" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="T323" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U323" s="1" t="inlineStr">
@@ -38017,7 +38017,7 @@
       </c>
       <c r="T324" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U324" s="1" t="inlineStr">
@@ -38137,7 +38137,7 @@
       </c>
       <c r="T325" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U325" s="1" t="inlineStr">
@@ -38257,7 +38257,7 @@
       </c>
       <c r="T326" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U326" s="1" t="inlineStr">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="T327" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U327" s="1" t="inlineStr">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="T328" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U328" s="1" t="inlineStr">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="T329" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U329" s="1" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="T330" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U330" s="1" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="T331" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U331" s="1" t="inlineStr">
@@ -38977,7 +38977,7 @@
       </c>
       <c r="T332" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U332" s="1" t="inlineStr">
@@ -39097,7 +39097,7 @@
       </c>
       <c r="T333" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U333" s="1" t="inlineStr">
@@ -39217,7 +39217,7 @@
       </c>
       <c r="T334" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U334" s="1" t="inlineStr">
@@ -39337,7 +39337,7 @@
       </c>
       <c r="T335" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U335" s="1" t="inlineStr">
@@ -39457,7 +39457,7 @@
       </c>
       <c r="T336" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U336" s="1" t="inlineStr">
@@ -39577,7 +39577,7 @@
       </c>
       <c r="T337" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U337" s="1" t="inlineStr">
@@ -39697,7 +39697,7 @@
       </c>
       <c r="T338" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U338" s="1" t="inlineStr">
@@ -39817,7 +39817,7 @@
       </c>
       <c r="T339" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U339" s="1" t="inlineStr">
@@ -39937,7 +39937,7 @@
       </c>
       <c r="T340" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U340" s="1" t="inlineStr">
@@ -40057,7 +40057,7 @@
       </c>
       <c r="T341" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U341" s="1" t="inlineStr">
@@ -40177,7 +40177,7 @@
       </c>
       <c r="T342" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U342" s="1" t="inlineStr">
@@ -40297,7 +40297,7 @@
       </c>
       <c r="T343" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U343" s="1" t="inlineStr">
@@ -40417,7 +40417,7 @@
       </c>
       <c r="T344" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U344" s="1" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="T345" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U345" s="1" t="inlineStr">
@@ -40657,7 +40657,7 @@
       </c>
       <c r="T346" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U346" s="1" t="inlineStr">
@@ -40777,7 +40777,7 @@
       </c>
       <c r="T347" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U347" s="1" t="inlineStr">
@@ -40897,7 +40897,7 @@
       </c>
       <c r="T348" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U348" s="1" t="inlineStr">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="T349" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U349" s="1" t="inlineStr">
@@ -41137,7 +41137,7 @@
       </c>
       <c r="T350" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U350" s="1" t="inlineStr">
@@ -41257,7 +41257,7 @@
       </c>
       <c r="T351" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U351" s="1" t="inlineStr">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="T352" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U352" s="1" t="inlineStr">
@@ -41497,7 +41497,7 @@
       </c>
       <c r="T353" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U353" s="1" t="inlineStr">
@@ -41617,7 +41617,7 @@
       </c>
       <c r="T354" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U354" s="1" t="inlineStr">
@@ -41737,7 +41737,7 @@
       </c>
       <c r="T355" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U355" s="1" t="inlineStr">
@@ -41857,7 +41857,7 @@
       </c>
       <c r="T356" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U356" s="1" t="inlineStr">
@@ -41977,7 +41977,7 @@
       </c>
       <c r="T357" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U357" s="1" t="inlineStr">
@@ -42097,7 +42097,7 @@
       </c>
       <c r="T358" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U358" s="1" t="inlineStr">
@@ -42217,7 +42217,7 @@
       </c>
       <c r="T359" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U359" s="1" t="inlineStr">
@@ -42337,7 +42337,7 @@
       </c>
       <c r="T360" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U360" s="1" t="inlineStr">
@@ -42457,7 +42457,7 @@
       </c>
       <c r="T361" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U361" s="1" t="inlineStr">
@@ -42577,7 +42577,7 @@
       </c>
       <c r="T362" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U362" s="1" t="inlineStr">
@@ -42697,7 +42697,7 @@
       </c>
       <c r="T363" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U363" s="1" t="inlineStr">
@@ -42817,7 +42817,7 @@
       </c>
       <c r="T364" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U364" s="1" t="inlineStr">
@@ -42937,7 +42937,7 @@
       </c>
       <c r="T365" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U365" s="1" t="inlineStr">
@@ -43057,7 +43057,7 @@
       </c>
       <c r="T366" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U366" s="1" t="inlineStr">
@@ -43177,7 +43177,7 @@
       </c>
       <c r="T367" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U367" s="1" t="inlineStr">
@@ -43297,7 +43297,7 @@
       </c>
       <c r="T368" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U368" s="1" t="inlineStr">
@@ -43417,7 +43417,7 @@
       </c>
       <c r="T369" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U369" s="1" t="inlineStr">
@@ -43537,7 +43537,7 @@
       </c>
       <c r="T370" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U370" s="1" t="inlineStr">
@@ -43657,7 +43657,7 @@
       </c>
       <c r="T371" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U371" s="1" t="inlineStr">
@@ -43777,7 +43777,7 @@
       </c>
       <c r="T372" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U372" s="1" t="inlineStr">
@@ -43897,7 +43897,7 @@
       </c>
       <c r="T373" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U373" s="1" t="inlineStr">
@@ -44017,7 +44017,7 @@
       </c>
       <c r="T374" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U374" s="1" t="inlineStr">
@@ -44137,7 +44137,7 @@
       </c>
       <c r="T375" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U375" s="1" t="inlineStr">
@@ -44257,7 +44257,7 @@
       </c>
       <c r="T376" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U376" s="1" t="inlineStr">
@@ -44377,7 +44377,7 @@
       </c>
       <c r="T377" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U377" s="1" t="inlineStr">
@@ -44497,7 +44497,7 @@
       </c>
       <c r="T378" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U378" s="1" t="inlineStr">
@@ -44617,7 +44617,7 @@
       </c>
       <c r="T379" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U379" s="1" t="inlineStr">
@@ -44737,7 +44737,7 @@
       </c>
       <c r="T380" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U380" s="1" t="inlineStr">
@@ -44857,7 +44857,7 @@
       </c>
       <c r="T381" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U381" s="1" t="inlineStr">
@@ -44977,7 +44977,7 @@
       </c>
       <c r="T382" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U382" s="1" t="inlineStr">
@@ -45097,7 +45097,7 @@
       </c>
       <c r="T383" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U383" s="1" t="inlineStr">
@@ -45217,7 +45217,7 @@
       </c>
       <c r="T384" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U384" s="1" t="inlineStr">
@@ -45337,7 +45337,7 @@
       </c>
       <c r="T385" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U385" s="1" t="inlineStr">
@@ -45457,7 +45457,7 @@
       </c>
       <c r="T386" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U386" s="1" t="inlineStr">
@@ -45577,7 +45577,7 @@
       </c>
       <c r="T387" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U387" s="1" t="inlineStr">
@@ -45697,7 +45697,7 @@
       </c>
       <c r="T388" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U388" s="1" t="inlineStr">
@@ -45817,7 +45817,7 @@
       </c>
       <c r="T389" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U389" s="1" t="inlineStr">
@@ -45937,7 +45937,7 @@
       </c>
       <c r="T390" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U390" s="1" t="inlineStr">
@@ -46057,7 +46057,7 @@
       </c>
       <c r="T391" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U391" s="1" t="inlineStr">
@@ -46177,7 +46177,7 @@
       </c>
       <c r="T392" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U392" s="1" t="inlineStr">
@@ -46297,7 +46297,7 @@
       </c>
       <c r="T393" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U393" s="1" t="inlineStr">
@@ -46417,7 +46417,7 @@
       </c>
       <c r="T394" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U394" s="1" t="inlineStr">
@@ -46537,7 +46537,7 @@
       </c>
       <c r="T395" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U395" s="1" t="inlineStr">
@@ -46657,7 +46657,7 @@
       </c>
       <c r="T396" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U396" s="1" t="inlineStr">
@@ -46777,7 +46777,7 @@
       </c>
       <c r="T397" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U397" s="1" t="inlineStr">
@@ -46897,7 +46897,7 @@
       </c>
       <c r="T398" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U398" s="1" t="inlineStr">
@@ -47017,7 +47017,7 @@
       </c>
       <c r="T399" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U399" s="1" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="T400" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U400" s="1" t="inlineStr">
@@ -47257,7 +47257,7 @@
       </c>
       <c r="T401" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U401" s="1" t="inlineStr">
@@ -47377,7 +47377,7 @@
       </c>
       <c r="T402" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U402" s="1" t="inlineStr">
@@ -47497,7 +47497,7 @@
       </c>
       <c r="T403" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U403" s="1" t="inlineStr">
@@ -47617,7 +47617,7 @@
       </c>
       <c r="T404" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U404" s="1" t="inlineStr">
@@ -47737,7 +47737,7 @@
       </c>
       <c r="T405" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U405" s="1" t="inlineStr">
@@ -47857,7 +47857,7 @@
       </c>
       <c r="T406" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U406" s="1" t="inlineStr">
@@ -47977,7 +47977,7 @@
       </c>
       <c r="T407" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U407" s="1" t="inlineStr">
@@ -48097,7 +48097,7 @@
       </c>
       <c r="T408" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U408" s="1" t="inlineStr">
@@ -48217,7 +48217,7 @@
       </c>
       <c r="T409" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U409" s="1" t="inlineStr">
@@ -48337,7 +48337,7 @@
       </c>
       <c r="T410" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U410" s="1" t="inlineStr">
@@ -48457,7 +48457,7 @@
       </c>
       <c r="T411" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U411" s="1" t="inlineStr">
@@ -48577,7 +48577,7 @@
       </c>
       <c r="T412" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U412" s="1" t="inlineStr">
@@ -48697,7 +48697,7 @@
       </c>
       <c r="T413" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U413" s="1" t="inlineStr">
@@ -48817,7 +48817,7 @@
       </c>
       <c r="T414" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U414" s="1" t="inlineStr">
@@ -48937,7 +48937,7 @@
       </c>
       <c r="T415" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U415" s="1" t="inlineStr">
@@ -49057,7 +49057,7 @@
       </c>
       <c r="T416" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U416" s="1" t="inlineStr">
@@ -49177,7 +49177,7 @@
       </c>
       <c r="T417" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U417" s="1" t="inlineStr">
@@ -49297,7 +49297,7 @@
       </c>
       <c r="T418" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U418" s="1" t="inlineStr">
@@ -49417,7 +49417,7 @@
       </c>
       <c r="T419" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U419" s="1" t="inlineStr">
@@ -49537,7 +49537,7 @@
       </c>
       <c r="T420" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U420" s="1" t="inlineStr">
@@ -49657,7 +49657,7 @@
       </c>
       <c r="T421" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U421" s="1" t="inlineStr">
@@ -49777,7 +49777,7 @@
       </c>
       <c r="T422" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U422" s="1" t="inlineStr">
@@ -49897,7 +49897,7 @@
       </c>
       <c r="T423" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U423" s="1" t="inlineStr">
@@ -50017,7 +50017,7 @@
       </c>
       <c r="T424" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U424" s="1" t="inlineStr">
@@ -50137,7 +50137,7 @@
       </c>
       <c r="T425" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U425" s="1" t="inlineStr">
@@ -50257,7 +50257,7 @@
       </c>
       <c r="T426" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U426" s="1" t="inlineStr">
@@ -50377,7 +50377,7 @@
       </c>
       <c r="T427" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U427" s="1" t="inlineStr">
@@ -50497,7 +50497,7 @@
       </c>
       <c r="T428" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U428" s="1" t="inlineStr">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="T429" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U429" s="1" t="inlineStr">
@@ -50737,7 +50737,7 @@
       </c>
       <c r="T430" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U430" s="1" t="inlineStr">
@@ -50857,7 +50857,7 @@
       </c>
       <c r="T431" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U431" s="1" t="inlineStr">
@@ -50977,7 +50977,7 @@
       </c>
       <c r="T432" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U432" s="1" t="inlineStr">
@@ -51097,7 +51097,7 @@
       </c>
       <c r="T433" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U433" s="1" t="inlineStr">
@@ -51217,7 +51217,7 @@
       </c>
       <c r="T434" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U434" s="1" t="inlineStr">
@@ -51337,7 +51337,7 @@
       </c>
       <c r="T435" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U435" s="1" t="inlineStr">
@@ -51457,7 +51457,7 @@
       </c>
       <c r="T436" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U436" s="1" t="inlineStr">
@@ -51577,7 +51577,7 @@
       </c>
       <c r="T437" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U437" s="1" t="inlineStr">
@@ -51697,7 +51697,7 @@
       </c>
       <c r="T438" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U438" s="1" t="inlineStr">
@@ -51817,7 +51817,7 @@
       </c>
       <c r="T439" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U439" s="1" t="inlineStr">
@@ -51937,7 +51937,7 @@
       </c>
       <c r="T440" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U440" s="1" t="inlineStr">
@@ -52057,7 +52057,7 @@
       </c>
       <c r="T441" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U441" s="1" t="inlineStr">
@@ -52177,7 +52177,7 @@
       </c>
       <c r="T442" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U442" s="1" t="inlineStr">
@@ -52297,7 +52297,7 @@
       </c>
       <c r="T443" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U443" s="1" t="inlineStr">
@@ -52417,7 +52417,7 @@
       </c>
       <c r="T444" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U444" s="1" t="inlineStr">
@@ -52537,7 +52537,7 @@
       </c>
       <c r="T445" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U445" s="1" t="inlineStr">
@@ -52657,7 +52657,7 @@
       </c>
       <c r="T446" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U446" s="1" t="inlineStr">
@@ -52777,7 +52777,7 @@
       </c>
       <c r="T447" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U447" s="1" t="inlineStr">
@@ -52897,7 +52897,7 @@
       </c>
       <c r="T448" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U448" s="1" t="inlineStr">
@@ -53017,7 +53017,7 @@
       </c>
       <c r="T449" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U449" s="1" t="inlineStr">
@@ -53137,7 +53137,7 @@
       </c>
       <c r="T450" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U450" s="1" t="inlineStr">
@@ -53257,7 +53257,7 @@
       </c>
       <c r="T451" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U451" s="1" t="inlineStr">
@@ -53377,7 +53377,7 @@
       </c>
       <c r="T452" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U452" s="1" t="inlineStr">
@@ -53497,7 +53497,7 @@
       </c>
       <c r="T453" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U453" s="1" t="inlineStr">
@@ -53617,7 +53617,7 @@
       </c>
       <c r="T454" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U454" s="1" t="inlineStr">
@@ -53737,7 +53737,7 @@
       </c>
       <c r="T455" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U455" s="1" t="inlineStr">
@@ -53857,7 +53857,7 @@
       </c>
       <c r="T456" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U456" s="1" t="inlineStr">
@@ -53977,7 +53977,7 @@
       </c>
       <c r="T457" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U457" s="1" t="inlineStr">
@@ -54097,7 +54097,7 @@
       </c>
       <c r="T458" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U458" s="1" t="inlineStr">
@@ -54217,7 +54217,7 @@
       </c>
       <c r="T459" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U459" s="1" t="inlineStr">
@@ -54337,7 +54337,7 @@
       </c>
       <c r="T460" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U460" s="1" t="inlineStr">
@@ -54457,7 +54457,7 @@
       </c>
       <c r="T461" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U461" s="1" t="inlineStr">
@@ -54577,7 +54577,7 @@
       </c>
       <c r="T462" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U462" s="1" t="inlineStr">
@@ -54697,7 +54697,7 @@
       </c>
       <c r="T463" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U463" s="1" t="inlineStr">
@@ -54817,7 +54817,7 @@
       </c>
       <c r="T464" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U464" s="1" t="inlineStr">
@@ -54937,7 +54937,7 @@
       </c>
       <c r="T465" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U465" s="1" t="inlineStr">
@@ -55401,7 +55401,7 @@
       </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U2" s="1" t="inlineStr">
@@ -55509,7 +55509,7 @@
       </c>
       <c r="T3" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U3" s="1" t="inlineStr">
@@ -55617,7 +55617,7 @@
       </c>
       <c r="T4" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U4" s="1" t="inlineStr">
@@ -55725,7 +55725,7 @@
       </c>
       <c r="T5" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U5" s="1" t="inlineStr">
@@ -55833,7 +55833,7 @@
       </c>
       <c r="T6" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U6" s="1" t="inlineStr">
@@ -55941,7 +55941,7 @@
       </c>
       <c r="T7" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U7" s="1" t="inlineStr">
@@ -56049,7 +56049,7 @@
       </c>
       <c r="T8" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U8" s="1" t="inlineStr">
@@ -56157,7 +56157,7 @@
       </c>
       <c r="T9" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U9" s="1" t="inlineStr">
@@ -56265,7 +56265,7 @@
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U10" s="1" t="inlineStr">
@@ -56373,7 +56373,7 @@
       </c>
       <c r="T11" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U11" s="1" t="inlineStr">
@@ -56481,7 +56481,7 @@
       </c>
       <c r="T12" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U12" s="1" t="inlineStr">
@@ -56589,7 +56589,7 @@
       </c>
       <c r="T13" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U13" s="1" t="inlineStr">
@@ -56697,7 +56697,7 @@
       </c>
       <c r="T14" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
@@ -56805,7 +56805,7 @@
       </c>
       <c r="T15" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U15" s="1" t="inlineStr">
@@ -56913,7 +56913,7 @@
       </c>
       <c r="T16" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U16" s="1" t="inlineStr">
@@ -57021,7 +57021,7 @@
       </c>
       <c r="T17" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U17" s="1" t="inlineStr">
@@ -57129,7 +57129,7 @@
       </c>
       <c r="T18" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U18" s="1" t="inlineStr">
@@ -57237,7 +57237,7 @@
       </c>
       <c r="T19" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -57345,7 +57345,7 @@
       </c>
       <c r="T20" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U20" s="1" t="inlineStr">
@@ -57453,7 +57453,7 @@
       </c>
       <c r="T21" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U21" s="1" t="inlineStr">
@@ -57561,7 +57561,7 @@
       </c>
       <c r="T22" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U22" s="1" t="inlineStr">
@@ -57669,7 +57669,7 @@
       </c>
       <c r="T23" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U23" s="1" t="inlineStr">
@@ -57777,7 +57777,7 @@
       </c>
       <c r="T24" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U24" s="1" t="inlineStr">
@@ -57885,7 +57885,7 @@
       </c>
       <c r="T25" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U25" s="1" t="inlineStr">
@@ -57993,7 +57993,7 @@
       </c>
       <c r="T26" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U26" s="1" t="inlineStr">
@@ -58101,7 +58101,7 @@
       </c>
       <c r="T27" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U27" s="1" t="inlineStr">
@@ -58209,7 +58209,7 @@
       </c>
       <c r="T28" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U28" s="1" t="inlineStr">
@@ -58317,7 +58317,7 @@
       </c>
       <c r="T29" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U29" s="1" t="inlineStr">
@@ -58425,7 +58425,7 @@
       </c>
       <c r="T30" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U30" s="1" t="inlineStr">
@@ -58533,7 +58533,7 @@
       </c>
       <c r="T31" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U31" s="1" t="inlineStr">
@@ -58641,7 +58641,7 @@
       </c>
       <c r="T32" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U32" s="1" t="inlineStr">
@@ -58749,7 +58749,7 @@
       </c>
       <c r="T33" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U33" s="1" t="inlineStr">
@@ -58857,7 +58857,7 @@
       </c>
       <c r="T34" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U34" s="1" t="inlineStr">
@@ -58965,7 +58965,7 @@
       </c>
       <c r="T35" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U35" s="1" t="inlineStr">
@@ -59073,7 +59073,7 @@
       </c>
       <c r="T36" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U36" s="1" t="inlineStr">
@@ -59181,7 +59181,7 @@
       </c>
       <c r="T37" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U37" s="1" t="inlineStr">
@@ -59289,7 +59289,7 @@
       </c>
       <c r="T38" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U38" s="1" t="inlineStr">
@@ -59397,7 +59397,7 @@
       </c>
       <c r="T39" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U39" s="1" t="inlineStr">
@@ -59505,7 +59505,7 @@
       </c>
       <c r="T40" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U40" s="1" t="inlineStr">
@@ -59613,7 +59613,7 @@
       </c>
       <c r="T41" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U41" s="1" t="inlineStr">
@@ -59721,7 +59721,7 @@
       </c>
       <c r="T42" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U42" s="1" t="inlineStr">
@@ -59829,7 +59829,7 @@
       </c>
       <c r="T43" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U43" s="1" t="inlineStr">
@@ -59937,7 +59937,7 @@
       </c>
       <c r="T44" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U44" s="1" t="inlineStr">
@@ -60045,7 +60045,7 @@
       </c>
       <c r="T45" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U45" s="1" t="inlineStr">
@@ -60153,7 +60153,7 @@
       </c>
       <c r="T46" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U46" s="1" t="inlineStr">
@@ -60261,7 +60261,7 @@
       </c>
       <c r="T47" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U47" s="1" t="inlineStr">
@@ -60369,7 +60369,7 @@
       </c>
       <c r="T48" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U48" s="1" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="T49" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U49" s="1" t="inlineStr">
@@ -60585,7 +60585,7 @@
       </c>
       <c r="T50" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U50" s="1" t="inlineStr">
@@ -60693,7 +60693,7 @@
       </c>
       <c r="T51" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U51" s="1" t="inlineStr">
@@ -60801,7 +60801,7 @@
       </c>
       <c r="T52" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U52" s="1" t="inlineStr">
@@ -60909,7 +60909,7 @@
       </c>
       <c r="T53" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U53" s="1" t="inlineStr">
@@ -61017,7 +61017,7 @@
       </c>
       <c r="T54" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U54" s="1" t="inlineStr">
@@ -61125,7 +61125,7 @@
       </c>
       <c r="T55" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U55" s="1" t="inlineStr">
@@ -61233,7 +61233,7 @@
       </c>
       <c r="T56" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U56" s="1" t="inlineStr">
@@ -61341,7 +61341,7 @@
       </c>
       <c r="T57" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U57" s="1" t="inlineStr">
@@ -61449,7 +61449,7 @@
       </c>
       <c r="T58" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U58" s="1" t="inlineStr">
@@ -61557,7 +61557,7 @@
       </c>
       <c r="T59" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U59" s="1" t="inlineStr">
@@ -61665,7 +61665,7 @@
       </c>
       <c r="T60" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U60" s="1" t="inlineStr">
@@ -61773,7 +61773,7 @@
       </c>
       <c r="T61" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U61" s="1" t="inlineStr">
@@ -61881,7 +61881,7 @@
       </c>
       <c r="T62" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U62" s="1" t="inlineStr">
@@ -61989,7 +61989,7 @@
       </c>
       <c r="T63" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U63" s="1" t="inlineStr">
@@ -62097,7 +62097,7 @@
       </c>
       <c r="T64" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U64" s="1" t="inlineStr">
@@ -62205,7 +62205,7 @@
       </c>
       <c r="T65" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U65" s="1" t="inlineStr">
@@ -62313,7 +62313,7 @@
       </c>
       <c r="T66" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U66" s="1" t="inlineStr">
@@ -62421,7 +62421,7 @@
       </c>
       <c r="T67" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U67" s="1" t="inlineStr">
@@ -62529,7 +62529,7 @@
       </c>
       <c r="T68" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U68" s="1" t="inlineStr">
@@ -62637,7 +62637,7 @@
       </c>
       <c r="T69" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U69" s="1" t="inlineStr">
@@ -62745,7 +62745,7 @@
       </c>
       <c r="T70" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U70" s="1" t="inlineStr">
@@ -62853,7 +62853,7 @@
       </c>
       <c r="T71" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U71" s="1" t="inlineStr">
@@ -62961,7 +62961,7 @@
       </c>
       <c r="T72" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U72" s="1" t="inlineStr">
@@ -63069,7 +63069,7 @@
       </c>
       <c r="T73" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U73" s="1" t="inlineStr">
@@ -63177,7 +63177,7 @@
       </c>
       <c r="T74" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U74" s="1" t="inlineStr">
@@ -63285,7 +63285,7 @@
       </c>
       <c r="T75" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U75" s="1" t="inlineStr">
@@ -63393,7 +63393,7 @@
       </c>
       <c r="T76" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U76" s="1" t="inlineStr">
@@ -63501,7 +63501,7 @@
       </c>
       <c r="T77" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U77" s="1" t="inlineStr">
@@ -63609,7 +63609,7 @@
       </c>
       <c r="T78" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U78" s="1" t="inlineStr">
@@ -63717,7 +63717,7 @@
       </c>
       <c r="T79" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U79" s="1" t="inlineStr">
@@ -63825,7 +63825,7 @@
       </c>
       <c r="T80" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U80" s="1" t="inlineStr">
@@ -63933,7 +63933,7 @@
       </c>
       <c r="T81" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U81" s="1" t="inlineStr">
@@ -64041,7 +64041,7 @@
       </c>
       <c r="T82" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U82" s="1" t="inlineStr">
@@ -64149,7 +64149,7 @@
       </c>
       <c r="T83" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U83" s="1" t="inlineStr">
@@ -64257,7 +64257,7 @@
       </c>
       <c r="T84" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U84" s="1" t="inlineStr">
@@ -64365,7 +64365,7 @@
       </c>
       <c r="T85" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U85" s="1" t="inlineStr">
@@ -64473,7 +64473,7 @@
       </c>
       <c r="T86" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U86" s="1" t="inlineStr">
@@ -64581,7 +64581,7 @@
       </c>
       <c r="T87" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U87" s="1" t="inlineStr">
@@ -64689,7 +64689,7 @@
       </c>
       <c r="T88" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U88" s="1" t="inlineStr">
@@ -64797,7 +64797,7 @@
       </c>
       <c r="T89" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U89" s="1" t="inlineStr">
@@ -64905,7 +64905,7 @@
       </c>
       <c r="T90" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U90" s="1" t="inlineStr">
@@ -65013,7 +65013,7 @@
       </c>
       <c r="T91" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U91" s="1" t="inlineStr">
@@ -65121,7 +65121,7 @@
       </c>
       <c r="T92" s="1" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="U92" s="1" t="inlineStr">
